--- a/data/Companies_reports/Centerra Gold Inc/Data.xlsx
+++ b/data/Companies_reports/Centerra Gold Inc/Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca0-my.sharepoint.com/personal/marin_pellan_polymtlus_ca/Documents/Desktop/POST_DOC/Project/canada_metal_sustainability_db/data/Companies_reports/Centerra Gold Inc/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/metallican_db/data/Companies_reports/Centerra Gold Inc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_B15938E66CB69BDA039A7C40EAFF6950F69919D9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_B15938E66CB69BDA039A7C40EAFF6950F69919D9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCD0CE29-6820-4274-84D2-470974F68AF5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Balance Sheet (Y)" sheetId="1" r:id="rId1"/>
@@ -22,17 +22,30 @@
     <sheet name="Non-GAAP Measures (Y)" sheetId="7" r:id="rId7"/>
     <sheet name="Non-GAAP Measures (Q)" sheetId="8" r:id="rId8"/>
     <sheet name="Mount Milligan (Y)" sheetId="9" r:id="rId9"/>
-    <sheet name="Mount Milligan (Q)" sheetId="10" r:id="rId10"/>
-    <sheet name="Öksüt (Q)" sheetId="11" r:id="rId11"/>
-    <sheet name="Öksüt (Y)" sheetId="12" r:id="rId12"/>
-    <sheet name="Molybdenum (Y)" sheetId="13" r:id="rId13"/>
+    <sheet name="Öksüt (Q)" sheetId="11" r:id="rId10"/>
+    <sheet name="Öksüt (Y)" sheetId="12" r:id="rId11"/>
+    <sheet name="Molybdenum (Y)" sheetId="13" r:id="rId12"/>
+    <sheet name="Mount Milligan (Q)" sheetId="10" r:id="rId13"/>
     <sheet name="Molybdenum (Q)" sheetId="14" r:id="rId14"/>
     <sheet name="Governance" sheetId="15" r:id="rId15"/>
     <sheet name="Social" sheetId="16" r:id="rId16"/>
     <sheet name="Environmental" sheetId="17" r:id="rId17"/>
     <sheet name="Reserves &amp; Resources (Y)" sheetId="18" r:id="rId18"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2142,14 +2155,14 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(&quot;&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="0.00%;\ \(0.00%\)"/>
     <numFmt numFmtId="167" formatCode="##,##0.;\ \(##,##0.\)"/>
-    <numFmt numFmtId="169" formatCode="##,##0.0;\ \(##,##0.0\)"/>
-    <numFmt numFmtId="170" formatCode="0.0%;\ \(0.0%\)"/>
-    <numFmt numFmtId="171" formatCode="##,##0.000;\ \(##,##0.000\)"/>
-    <numFmt numFmtId="172" formatCode="0.000%;\ \(0.000%\)"/>
-    <numFmt numFmtId="179" formatCode="##,##0;\ \(##,##0\)"/>
-    <numFmt numFmtId="180" formatCode="##0.00;\ \(##0.00\)"/>
-    <numFmt numFmtId="181" formatCode="##0;\ \(##0\)"/>
-    <numFmt numFmtId="182" formatCode="0%;\ \(0%\)"/>
+    <numFmt numFmtId="168" formatCode="##,##0.0;\ \(##,##0.0\)"/>
+    <numFmt numFmtId="169" formatCode="0.0%;\ \(0.0%\)"/>
+    <numFmt numFmtId="170" formatCode="##,##0.000;\ \(##,##0.000\)"/>
+    <numFmt numFmtId="171" formatCode="0.000%;\ \(0.000%\)"/>
+    <numFmt numFmtId="172" formatCode="##,##0;\ \(##,##0\)"/>
+    <numFmt numFmtId="173" formatCode="##0.00;\ \(##0.00\)"/>
+    <numFmt numFmtId="174" formatCode="##0;\ \(##0\)"/>
+    <numFmt numFmtId="175" formatCode="0%;\ \(0%\)"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -2355,7 +2368,7 @@
     <xf numFmtId="167" fontId="2" fillId="0" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="4" borderId="1">
+    <xf numFmtId="172" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="4" borderId="1">
@@ -2370,10 +2383,10 @@
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="4" borderId="1">
+    <xf numFmtId="172" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="6" borderId="1">
+    <xf numFmtId="172" fontId="4" fillId="6" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1">
@@ -2385,16 +2398,16 @@
     <xf numFmtId="165" fontId="5" fillId="4" borderId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="4" borderId="1">
+    <xf numFmtId="172" fontId="5" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="4" borderId="1">
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="4" borderId="1">
+    <xf numFmtId="172" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="6" borderId="1">
+    <xf numFmtId="168" fontId="4" fillId="6" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1">
@@ -2433,13 +2446,13 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="4" borderId="1">
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="left" vertical="top" indent="2"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="4" borderId="1">
+    <xf numFmtId="168" fontId="5" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1">
@@ -2451,10 +2464,10 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="7" borderId="1">
+    <xf numFmtId="172" fontId="4" fillId="7" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="7" borderId="1">
+    <xf numFmtId="172" fontId="5" fillId="7" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1">
@@ -2481,37 +2494,37 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="6" borderId="1">
+    <xf numFmtId="172" fontId="4" fillId="6" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="4" borderId="1">
+    <xf numFmtId="173" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="4" borderId="1">
+    <xf numFmtId="173" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="7" borderId="1">
+    <xf numFmtId="172" fontId="4" fillId="7" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="4" borderId="1">
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="4" borderId="1">
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="4" borderId="1">
+    <xf numFmtId="172" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="4" borderId="1">
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="4" borderId="1">
+    <xf numFmtId="172" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1">
@@ -2526,13 +2539,13 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="7" borderId="1">
+    <xf numFmtId="168" fontId="4" fillId="7" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="4" borderId="1">
+    <xf numFmtId="172" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1">
@@ -2550,31 +2563,31 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="4" borderId="1">
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="4" borderId="1">
+    <xf numFmtId="172" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="4" borderId="1">
+    <xf numFmtId="172" fontId="5" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="4" borderId="1">
+    <xf numFmtId="168" fontId="5" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="4" borderId="1">
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="4" borderId="1">
+    <xf numFmtId="173" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="4" borderId="1">
+    <xf numFmtId="172" fontId="5" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="4" borderId="1">
+    <xf numFmtId="168" fontId="5" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1">
@@ -2592,7 +2605,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="left" vertical="top" indent="2"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="4" borderId="1">
+    <xf numFmtId="172" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1">
@@ -2607,13 +2620,13 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="7" borderId="1">
+    <xf numFmtId="172" fontId="4" fillId="7" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="7" borderId="1">
+    <xf numFmtId="173" fontId="4" fillId="7" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="7" borderId="1">
@@ -2625,25 +2638,25 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="left" vertical="top" indent="4"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="4" borderId="1">
+    <xf numFmtId="173" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="4" borderId="1">
+    <xf numFmtId="172" fontId="5" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="7" borderId="1">
+    <xf numFmtId="168" fontId="5" fillId="7" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="4" borderId="1">
+    <xf numFmtId="172" fontId="4" fillId="4" borderId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="4" borderId="1">
+    <xf numFmtId="172" fontId="4" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="4" borderId="1">
+    <xf numFmtId="172" fontId="5" fillId="4" borderId="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellStyleXfs>
@@ -2675,14 +2688,14 @@
       <alignment horizontal="left" indent="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="179" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -2697,7 +2710,7 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="180" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2714,7 +2727,7 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="179" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="172" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2728,21 +2741,21 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="169" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2751,7 +2764,7 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2763,7 +2776,7 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="181" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2775,10 +2788,10 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="172" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4460,14 +4473,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7BF9D54-8163-AD42-0B98-40BCDDEF5B4E}">
   <dimension ref="A1:F47"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.36328125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="25" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="66.6640625" style="13" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="66.6328125" style="13" customWidth="1" collapsed="1"/>
     <col min="4" max="6" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4487,7 +4500,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
@@ -4503,7 +4516,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
@@ -5255,16 +5268,16 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{696A46DF-C2E1-5DF4-52C8-FDF6064D6637}">
-  <dimension ref="A1:O70"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB012AFB-0069-B049-2769-3A59A928ED4A}">
+  <dimension ref="A1:O53"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.36328125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="25" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="66.6640625" style="13" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="66.6328125" style="13" customWidth="1" collapsed="1"/>
     <col min="4" max="15" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -5311,7 +5324,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
@@ -5354,2950 +5367,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="23"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
-    </row>
-    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-    </row>
-    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="D6" s="26">
-        <v>58.5</v>
-      </c>
-      <c r="E6" s="26">
-        <v>55.6</v>
-      </c>
-      <c r="F6" s="26">
-        <v>67.7</v>
-      </c>
-      <c r="G6" s="26">
-        <v>66.8</v>
-      </c>
-      <c r="H6" s="26">
-        <v>56.4</v>
-      </c>
-      <c r="I6" s="26">
-        <v>52.8</v>
-      </c>
-      <c r="J6" s="26">
-        <v>58.3</v>
-      </c>
-      <c r="K6" s="26">
-        <v>50.7</v>
-      </c>
-      <c r="L6" s="26">
-        <v>70</v>
-      </c>
-      <c r="M6" s="26">
-        <v>53.5</v>
-      </c>
-      <c r="N6" s="26">
-        <v>87.3</v>
-      </c>
-      <c r="O6" s="26">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="D7" s="26">
-        <v>73.3</v>
-      </c>
-      <c r="E7" s="26">
-        <v>41.5</v>
-      </c>
-      <c r="F7" s="26">
-        <v>49</v>
-      </c>
-      <c r="G7" s="26">
-        <v>52.7</v>
-      </c>
-      <c r="H7" s="26">
-        <v>52.4</v>
-      </c>
-      <c r="I7" s="26">
-        <v>32.9</v>
-      </c>
-      <c r="J7" s="26">
-        <v>46</v>
-      </c>
-      <c r="K7" s="26">
-        <v>49.7</v>
-      </c>
-      <c r="L7" s="26">
-        <v>48.7</v>
-      </c>
-      <c r="M7" s="26">
-        <v>44.4</v>
-      </c>
-      <c r="N7" s="26">
-        <v>47.8</v>
-      </c>
-      <c r="O7" s="26">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="D8" s="26">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="E8" s="26">
-        <v>1.9</v>
-      </c>
-      <c r="F8" s="26">
-        <v>1.5</v>
-      </c>
-      <c r="G8" s="26">
-        <v>1.7</v>
-      </c>
-      <c r="H8" s="26">
-        <v>2.1</v>
-      </c>
-      <c r="I8" s="26">
-        <v>1.8</v>
-      </c>
-      <c r="J8" s="26">
-        <v>2</v>
-      </c>
-      <c r="K8" s="26">
-        <v>2.1</v>
-      </c>
-      <c r="L8" s="26">
-        <v>1.7</v>
-      </c>
-      <c r="M8" s="26">
-        <v>1.9</v>
-      </c>
-      <c r="N8" s="26">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="O8" s="26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="D9" s="26">
-        <v>134.1</v>
-      </c>
-      <c r="E9" s="26">
-        <v>99</v>
-      </c>
-      <c r="F9" s="26">
-        <v>118.2</v>
-      </c>
-      <c r="G9" s="26">
-        <v>121.2</v>
-      </c>
-      <c r="H9" s="26">
-        <v>110.9</v>
-      </c>
-      <c r="I9" s="26">
-        <v>87.5</v>
-      </c>
-      <c r="J9" s="26">
-        <v>106.3</v>
-      </c>
-      <c r="K9" s="26">
-        <v>102.5</v>
-      </c>
-      <c r="L9" s="26">
-        <v>120.5</v>
-      </c>
-      <c r="M9" s="26">
-        <v>99.8</v>
-      </c>
-      <c r="N9" s="26">
-        <v>137.4</v>
-      </c>
-      <c r="O9" s="26">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" s="26">
-        <v>58.6</v>
-      </c>
-      <c r="E10" s="26">
-        <v>69.8</v>
-      </c>
-      <c r="F10" s="26">
-        <v>70.7</v>
-      </c>
-      <c r="G10" s="26">
-        <v>69.8</v>
-      </c>
-      <c r="H10" s="26">
-        <v>84.6</v>
-      </c>
-      <c r="I10" s="26">
-        <v>76.3</v>
-      </c>
-      <c r="J10" s="26">
-        <v>80.400000000000006</v>
-      </c>
-      <c r="K10" s="26">
-        <v>62.1</v>
-      </c>
-      <c r="L10" s="26">
-        <v>73</v>
-      </c>
-      <c r="M10" s="26">
-        <v>63.4</v>
-      </c>
-      <c r="N10" s="26">
-        <v>80.599999999999994</v>
-      </c>
-      <c r="O10" s="26">
-        <v>89.3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="D11" s="26">
-        <v>23.5</v>
-      </c>
-      <c r="E11" s="26">
-        <v>26.5</v>
-      </c>
-      <c r="F11" s="26">
-        <v>13.5</v>
-      </c>
-      <c r="G11" s="26">
-        <v>15.8</v>
-      </c>
-      <c r="H11" s="26">
-        <v>17.3</v>
-      </c>
-      <c r="I11" s="26">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="J11" s="26">
-        <v>21.5</v>
-      </c>
-      <c r="K11" s="26">
-        <v>17.899999999999999</v>
-      </c>
-      <c r="L11" s="26">
-        <v>18.3</v>
-      </c>
-      <c r="M11" s="26">
-        <v>14.1</v>
-      </c>
-      <c r="N11" s="26">
-        <v>19</v>
-      </c>
-      <c r="O11" s="26">
-        <v>21.4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" s="26">
-        <v>52</v>
-      </c>
-      <c r="E12" s="26">
-        <v>2.7</v>
-      </c>
-      <c r="F12" s="26">
-        <v>34</v>
-      </c>
-      <c r="G12" s="26">
-        <v>35.6</v>
-      </c>
-      <c r="H12" s="26">
-        <v>9</v>
-      </c>
-      <c r="I12" s="26">
-        <v>-8.6999999999999993</v>
-      </c>
-      <c r="J12" s="26">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="K12" s="26">
-        <v>22.5</v>
-      </c>
-      <c r="L12" s="26">
-        <v>29.2</v>
-      </c>
-      <c r="M12" s="26">
-        <v>22.3</v>
-      </c>
-      <c r="N12" s="26">
-        <v>37.799999999999997</v>
-      </c>
-      <c r="O12" s="26">
-        <v>27.3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="D13" s="26">
-        <v>45.6</v>
-      </c>
-      <c r="E13" s="26">
-        <v>-3.4</v>
-      </c>
-      <c r="F13" s="26">
-        <v>28.2</v>
-      </c>
-      <c r="G13" s="26">
-        <v>29.7</v>
-      </c>
-      <c r="H13" s="26">
-        <v>6.9</v>
-      </c>
-      <c r="I13" s="26">
-        <v>-12.6</v>
-      </c>
-      <c r="J13" s="26">
-        <v>-0.8</v>
-      </c>
-      <c r="K13" s="26">
-        <v>17.5</v>
-      </c>
-      <c r="L13" s="26">
-        <v>23.6</v>
-      </c>
-      <c r="M13" s="26">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="N13" s="26">
-        <v>29.4</v>
-      </c>
-      <c r="O13" s="26">
-        <v>55.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="D14" s="26">
-        <v>20.8</v>
-      </c>
-      <c r="E14" s="26">
-        <v>80.900000000000006</v>
-      </c>
-      <c r="F14" s="26">
-        <v>33.4</v>
-      </c>
-      <c r="G14" s="26">
-        <v>26.5</v>
-      </c>
-      <c r="H14" s="26">
-        <v>27.6</v>
-      </c>
-      <c r="I14" s="26">
-        <v>21.6</v>
-      </c>
-      <c r="J14" s="26">
-        <v>35.6</v>
-      </c>
-      <c r="K14" s="26">
-        <v>29.1</v>
-      </c>
-      <c r="L14" s="26">
-        <v>30</v>
-      </c>
-      <c r="M14" s="26">
-        <v>29</v>
-      </c>
-      <c r="N14" s="26">
-        <v>40.200000000000003</v>
-      </c>
-      <c r="O14" s="26">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="D15" s="26">
-        <v>6.4</v>
-      </c>
-      <c r="E15" s="26">
-        <v>57.5</v>
-      </c>
-      <c r="F15" s="26">
-        <v>20.9</v>
-      </c>
-      <c r="G15" s="26">
-        <v>15.6</v>
-      </c>
-      <c r="H15" s="26">
-        <v>24.6</v>
-      </c>
-      <c r="I15" s="26">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="J15" s="26">
-        <v>25.2</v>
-      </c>
-      <c r="K15" s="26">
-        <v>14.1</v>
-      </c>
-      <c r="L15" s="26">
-        <v>24.1</v>
-      </c>
-      <c r="M15" s="26">
-        <v>13.5</v>
-      </c>
-      <c r="N15" s="26">
-        <v>15.6</v>
-      </c>
-      <c r="O15" s="26">
-        <v>65.3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="D16" s="26">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="E16" s="26">
-        <v>18.3</v>
-      </c>
-      <c r="F16" s="26">
-        <v>6.6</v>
-      </c>
-      <c r="G16" s="26">
-        <v>14.6</v>
-      </c>
-      <c r="H16" s="26">
-        <v>4.3</v>
-      </c>
-      <c r="I16" s="26">
-        <v>11.9</v>
-      </c>
-      <c r="J16" s="26">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="K16" s="26">
-        <v>36.6</v>
-      </c>
-      <c r="L16" s="26">
-        <v>0.8</v>
-      </c>
-      <c r="M16" s="26">
-        <v>18.8</v>
-      </c>
-      <c r="N16" s="26">
-        <v>27.2</v>
-      </c>
-      <c r="O16" s="26">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="D17" s="26">
-        <v>13.4</v>
-      </c>
-      <c r="E17" s="26">
-        <v>20.9</v>
-      </c>
-      <c r="F17" s="26">
-        <v>10.4</v>
-      </c>
-      <c r="G17" s="26">
-        <v>10</v>
-      </c>
-      <c r="H17" s="26">
-        <v>1.8</v>
-      </c>
-      <c r="I17" s="26">
-        <v>13.3</v>
-      </c>
-      <c r="J17" s="26">
-        <v>12.5</v>
-      </c>
-      <c r="K17" s="26">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="L17" s="26">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="M17" s="26">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="N17" s="26">
-        <v>24.7</v>
-      </c>
-      <c r="O17" s="26">
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D18" s="26">
-        <v>12.5</v>
-      </c>
-      <c r="E18" s="26">
-        <v>20.3</v>
-      </c>
-      <c r="F18" s="26">
-        <v>10.4</v>
-      </c>
-      <c r="G18" s="26">
-        <v>9.9</v>
-      </c>
-      <c r="H18" s="26">
-        <v>1.8</v>
-      </c>
-      <c r="I18" s="26">
-        <v>13.3</v>
-      </c>
-      <c r="J18" s="26">
-        <v>12.5</v>
-      </c>
-      <c r="K18" s="26">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="L18" s="26">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="M18" s="26">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="N18" s="26">
-        <v>24.7</v>
-      </c>
-      <c r="O18" s="26">
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="D19" s="26">
-        <v>0.9</v>
-      </c>
-      <c r="E19" s="26">
-        <v>0.6</v>
-      </c>
-      <c r="F19" s="14">
-        <v>0</v>
-      </c>
-      <c r="G19" s="26">
-        <v>0.1</v>
-      </c>
-      <c r="H19" s="14">
-        <v>0</v>
-      </c>
-      <c r="I19" s="14">
-        <v>0</v>
-      </c>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="26"/>
-    </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-    </row>
-    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="D21" s="8">
-        <v>10651</v>
-      </c>
-      <c r="E21" s="8">
-        <v>11602</v>
-      </c>
-      <c r="F21" s="8">
-        <v>11924</v>
-      </c>
-      <c r="G21" s="8">
-        <v>10185</v>
-      </c>
-      <c r="H21" s="8">
-        <v>11321</v>
-      </c>
-      <c r="I21" s="8">
-        <v>12939</v>
-      </c>
-      <c r="J21" s="8">
-        <v>13357</v>
-      </c>
-      <c r="K21" s="8">
-        <v>12397</v>
-      </c>
-      <c r="L21" s="8">
-        <v>12332</v>
-      </c>
-      <c r="M21" s="8">
-        <v>12314</v>
-      </c>
-      <c r="N21" s="8">
-        <v>11801</v>
-      </c>
-      <c r="O21" s="8">
-        <v>9622</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="D22" s="8">
-        <v>4992</v>
-      </c>
-      <c r="E22" s="8">
-        <v>4556</v>
-      </c>
-      <c r="F22" s="8">
-        <v>5294</v>
-      </c>
-      <c r="G22" s="8">
-        <v>4578</v>
-      </c>
-      <c r="H22" s="8">
-        <v>3869</v>
-      </c>
-      <c r="I22" s="8">
-        <v>5252</v>
-      </c>
-      <c r="J22" s="8">
-        <v>5900</v>
-      </c>
-      <c r="K22" s="8">
-        <v>6256</v>
-      </c>
-      <c r="L22" s="8">
-        <v>5414</v>
-      </c>
-      <c r="M22" s="8">
-        <v>5605</v>
-      </c>
-      <c r="N22" s="8">
-        <v>5066</v>
-      </c>
-      <c r="O22" s="8">
-        <v>5844</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="D23" s="8">
-        <v>5251</v>
-      </c>
-      <c r="E23" s="8">
-        <v>5055</v>
-      </c>
-      <c r="F23" s="8">
-        <v>5538</v>
-      </c>
-      <c r="G23" s="8">
-        <v>5504</v>
-      </c>
-      <c r="H23" s="8">
-        <v>4705</v>
-      </c>
-      <c r="I23" s="8">
-        <v>5595</v>
-      </c>
-      <c r="J23" s="8">
-        <v>5605</v>
-      </c>
-      <c r="K23" s="8">
-        <v>5775</v>
-      </c>
-      <c r="L23" s="8">
-        <v>5162</v>
-      </c>
-      <c r="M23" s="8">
-        <v>5325</v>
-      </c>
-      <c r="N23" s="8">
-        <v>5553</v>
-      </c>
-      <c r="O23" s="8">
-        <v>5423</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="D24" s="27">
-        <v>0.35</v>
-      </c>
-      <c r="E24" s="27">
-        <v>0.39</v>
-      </c>
-      <c r="F24" s="27">
-        <v>0.47</v>
-      </c>
-      <c r="G24" s="27">
-        <v>0.47</v>
-      </c>
-      <c r="H24" s="27">
-        <v>0.34</v>
-      </c>
-      <c r="I24" s="27">
-        <v>0.38</v>
-      </c>
-      <c r="J24" s="27">
-        <v>0.35</v>
-      </c>
-      <c r="K24" s="27">
-        <v>0.35</v>
-      </c>
-      <c r="L24" s="27">
-        <v>0.46</v>
-      </c>
-      <c r="M24" s="27">
-        <v>0.36</v>
-      </c>
-      <c r="N24" s="27">
-        <v>0.4</v>
-      </c>
-      <c r="O24" s="27">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="D25" s="31">
-        <v>2.3E-3</v>
-      </c>
-      <c r="E25" s="31">
-        <v>2E-3</v>
-      </c>
-      <c r="F25" s="31">
-        <v>2E-3</v>
-      </c>
-      <c r="G25" s="31">
-        <v>1.9E-3</v>
-      </c>
-      <c r="H25" s="31">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="I25" s="31">
-        <v>1.6000000000000001E-3</v>
-      </c>
-      <c r="J25" s="31">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="K25" s="31">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="L25" s="31">
-        <v>1.8E-3</v>
-      </c>
-      <c r="M25" s="31">
-        <v>1.6000000000000001E-3</v>
-      </c>
-      <c r="N25" s="31">
-        <v>1.6000000000000001E-3</v>
-      </c>
-      <c r="O25" s="31">
-        <v>1.6000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="D26" s="32">
-        <v>0.67900000000000005</v>
-      </c>
-      <c r="E26" s="32">
-        <v>0.68799999999999994</v>
-      </c>
-      <c r="F26" s="32">
-        <v>0.66200000000000003</v>
-      </c>
-      <c r="G26" s="32">
-        <v>0.65500000000000003</v>
-      </c>
-      <c r="H26" s="32">
-        <v>0.65500000000000003</v>
-      </c>
-      <c r="I26" s="32">
-        <v>0.623</v>
-      </c>
-      <c r="J26" s="32">
-        <v>0.63700000000000001</v>
-      </c>
-      <c r="K26" s="32">
-        <v>0.64900000000000002</v>
-      </c>
-      <c r="L26" s="32">
-        <v>0.65600000000000003</v>
-      </c>
-      <c r="M26" s="32">
-        <v>0.64599999999999991</v>
-      </c>
-      <c r="N26" s="32">
-        <v>0.61399999999999999</v>
-      </c>
-      <c r="O26" s="32">
-        <v>0.59599999999999997</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="D27" s="32">
-        <v>0.81899999999999995</v>
-      </c>
-      <c r="E27" s="32">
-        <v>0.83699999999999997</v>
-      </c>
-      <c r="F27" s="32">
-        <v>0.82399999999999995</v>
-      </c>
-      <c r="G27" s="32">
-        <v>0.79500000000000004</v>
-      </c>
-      <c r="H27" s="32">
-        <v>0.78800000000000003</v>
-      </c>
-      <c r="I27" s="32">
-        <v>0.76100000000000001</v>
-      </c>
-      <c r="J27" s="32">
-        <v>0.76500000000000001</v>
-      </c>
-      <c r="K27" s="32">
-        <v>0.78700000000000003</v>
-      </c>
-      <c r="L27" s="32">
-        <v>0.76200000000000001</v>
-      </c>
-      <c r="M27" s="32">
-        <v>0.76900000000000002</v>
-      </c>
-      <c r="N27" s="32">
-        <v>0.73799999999999999</v>
-      </c>
-      <c r="O27" s="32">
-        <v>0.72400000000000009</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="D28" s="8">
-        <v>44932</v>
-      </c>
-      <c r="E28" s="8">
-        <v>39015</v>
-      </c>
-      <c r="F28" s="8">
-        <v>39749</v>
-      </c>
-      <c r="G28" s="8">
-        <v>40222</v>
-      </c>
-      <c r="H28" s="8">
-        <v>30524</v>
-      </c>
-      <c r="I28" s="8">
-        <v>32691</v>
-      </c>
-      <c r="J28" s="8">
-        <v>34265</v>
-      </c>
-      <c r="K28" s="8">
-        <v>44805</v>
-      </c>
-      <c r="L28" s="8">
-        <v>35402</v>
-      </c>
-      <c r="M28" s="8">
-        <v>35087</v>
-      </c>
-      <c r="N28" s="8">
-        <v>37131</v>
-      </c>
-      <c r="O28" s="8">
-        <v>32890</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="D29" s="8">
-        <v>39093</v>
-      </c>
-      <c r="E29" s="8">
-        <v>42728</v>
-      </c>
-      <c r="F29" s="8">
-        <v>54134</v>
-      </c>
-      <c r="G29" s="8">
-        <v>53222</v>
-      </c>
-      <c r="H29" s="8">
-        <v>33215</v>
-      </c>
-      <c r="I29" s="8">
-        <v>41119</v>
-      </c>
-      <c r="J29" s="8">
-        <v>39554</v>
-      </c>
-      <c r="K29" s="8">
-        <v>40503</v>
-      </c>
-      <c r="L29" s="8">
-        <v>48317</v>
-      </c>
-      <c r="M29" s="8">
-        <v>38609</v>
-      </c>
-      <c r="N29" s="8">
-        <v>42993</v>
-      </c>
-      <c r="O29" s="8">
-        <v>37660</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="D30" s="8">
-        <v>20558</v>
-      </c>
-      <c r="E30" s="8">
-        <v>17352</v>
-      </c>
-      <c r="F30" s="8">
-        <v>19045</v>
-      </c>
-      <c r="G30" s="8">
-        <v>16909</v>
-      </c>
-      <c r="H30" s="8">
-        <v>13355</v>
-      </c>
-      <c r="I30" s="8">
-        <v>13787</v>
-      </c>
-      <c r="J30" s="8">
-        <v>15026</v>
-      </c>
-      <c r="K30" s="8">
-        <v>19695</v>
-      </c>
-      <c r="L30" s="8">
-        <v>14331</v>
-      </c>
-      <c r="M30" s="8">
-        <v>13549</v>
-      </c>
-      <c r="N30" s="8">
-        <v>13694</v>
-      </c>
-      <c r="O30" s="8">
-        <v>12769</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="D31" s="8">
-        <v>40204</v>
-      </c>
-      <c r="E31" s="8">
-        <v>41597</v>
-      </c>
-      <c r="F31" s="8">
-        <v>56245</v>
-      </c>
-      <c r="G31" s="8">
-        <v>49444</v>
-      </c>
-      <c r="H31" s="8">
-        <v>38990</v>
-      </c>
-      <c r="I31" s="8">
-        <v>37470</v>
-      </c>
-      <c r="J31" s="8">
-        <v>42873</v>
-      </c>
-      <c r="K31" s="8">
-        <v>33127</v>
-      </c>
-      <c r="L31" s="8">
-        <v>45132</v>
-      </c>
-      <c r="M31" s="8">
-        <v>31402</v>
-      </c>
-      <c r="N31" s="8">
-        <v>45968</v>
-      </c>
-      <c r="O31" s="8">
-        <v>47887</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="D32" s="8">
-        <v>19449</v>
-      </c>
-      <c r="E32" s="8">
-        <v>18923</v>
-      </c>
-      <c r="F32" s="8">
-        <v>19647</v>
-      </c>
-      <c r="G32" s="8">
-        <v>15374</v>
-      </c>
-      <c r="H32" s="8">
-        <v>15332</v>
-      </c>
-      <c r="I32" s="8">
-        <v>12831</v>
-      </c>
-      <c r="J32" s="8">
-        <v>15385</v>
-      </c>
-      <c r="K32" s="8">
-        <v>16562</v>
-      </c>
-      <c r="L32" s="8">
-        <v>15622</v>
-      </c>
-      <c r="M32" s="8">
-        <v>11705</v>
-      </c>
-      <c r="N32" s="8">
-        <v>14209</v>
-      </c>
-      <c r="O32" s="8">
-        <v>16361</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="D33" s="8">
-        <v>1456</v>
-      </c>
-      <c r="E33" s="8">
-        <v>1335</v>
-      </c>
-      <c r="F33" s="8">
-        <v>1204</v>
-      </c>
-      <c r="G33" s="8">
-        <v>1352</v>
-      </c>
-      <c r="H33" s="8">
-        <v>1446</v>
-      </c>
-      <c r="I33" s="8">
-        <v>1410</v>
-      </c>
-      <c r="J33" s="8">
-        <v>1360</v>
-      </c>
-      <c r="K33" s="8">
-        <v>1529</v>
-      </c>
-      <c r="L33" s="8">
-        <v>1552</v>
-      </c>
-      <c r="M33" s="8">
-        <v>1703</v>
-      </c>
-      <c r="N33" s="8">
-        <v>1899</v>
-      </c>
-      <c r="O33" s="8">
-        <v>1864</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="D34" s="27">
-        <v>3.77</v>
-      </c>
-      <c r="E34" s="27">
-        <v>2.19</v>
-      </c>
-      <c r="F34" s="27">
-        <v>2.4900000000000002</v>
-      </c>
-      <c r="G34" s="27">
-        <v>3.43</v>
-      </c>
-      <c r="H34" s="27">
-        <v>3.42</v>
-      </c>
-      <c r="I34" s="27">
-        <v>2.56</v>
-      </c>
-      <c r="J34" s="27">
-        <v>2.99</v>
-      </c>
-      <c r="K34" s="27">
-        <v>3</v>
-      </c>
-      <c r="L34" s="27">
-        <v>3.12</v>
-      </c>
-      <c r="M34" s="27">
-        <v>3.79</v>
-      </c>
-      <c r="N34" s="27">
-        <v>3.37</v>
-      </c>
-      <c r="O34" s="27">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
-      <c r="L35" s="5"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
-      <c r="O35" s="5"/>
-    </row>
-    <row r="36" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="D36" s="8">
-        <v>647</v>
-      </c>
-      <c r="E36" s="8">
-        <v>961</v>
-      </c>
-      <c r="F36" s="8">
-        <v>729</v>
-      </c>
-      <c r="G36" s="8">
-        <v>790</v>
-      </c>
-      <c r="H36" s="8">
-        <v>1124</v>
-      </c>
-      <c r="I36" s="8">
-        <v>1255</v>
-      </c>
-      <c r="J36" s="8">
-        <v>1050</v>
-      </c>
-      <c r="K36" s="8">
-        <v>946</v>
-      </c>
-      <c r="L36" s="8">
-        <v>954</v>
-      </c>
-      <c r="M36" s="8">
-        <v>1102</v>
-      </c>
-      <c r="N36" s="8">
-        <v>1138</v>
-      </c>
-      <c r="O36" s="8">
-        <v>1219</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="D37" s="8">
-        <v>15</v>
-      </c>
-      <c r="E37" s="8">
-        <v>1245</v>
-      </c>
-      <c r="F37" s="8">
-        <v>615</v>
-      </c>
-      <c r="G37" s="8">
-        <v>629</v>
-      </c>
-      <c r="H37" s="8">
-        <v>914</v>
-      </c>
-      <c r="I37" s="8">
-        <v>1599</v>
-      </c>
-      <c r="J37" s="8">
-        <v>1150</v>
-      </c>
-      <c r="K37" s="8">
-        <v>946</v>
-      </c>
-      <c r="L37" s="8">
-        <v>688</v>
-      </c>
-      <c r="M37" s="8">
-        <v>1234</v>
-      </c>
-      <c r="N37" s="8">
-        <v>1318</v>
-      </c>
-      <c r="O37" s="8">
-        <v>1114</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="D38" s="8">
-        <v>819</v>
-      </c>
-      <c r="E38" s="8">
-        <v>1286</v>
-      </c>
-      <c r="F38" s="8">
-        <v>865</v>
-      </c>
-      <c r="G38" s="8">
-        <v>950</v>
-      </c>
-      <c r="H38" s="8">
-        <v>1134</v>
-      </c>
-      <c r="I38" s="8">
-        <v>1529</v>
-      </c>
-      <c r="J38" s="8">
-        <v>1245</v>
-      </c>
-      <c r="K38" s="8">
-        <v>1237</v>
-      </c>
-      <c r="L38" s="8">
-        <v>1044</v>
-      </c>
-      <c r="M38" s="8">
-        <v>1449</v>
-      </c>
-      <c r="N38" s="8">
-        <v>1526</v>
-      </c>
-      <c r="O38" s="8">
-        <v>1374</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="D39" s="27">
-        <v>1.68</v>
-      </c>
-      <c r="E39" s="27">
-        <v>1.58</v>
-      </c>
-      <c r="F39" s="27">
-        <v>1.51</v>
-      </c>
-      <c r="G39" s="27">
-        <v>2</v>
-      </c>
-      <c r="H39" s="27">
-        <v>2.66</v>
-      </c>
-      <c r="I39" s="27">
-        <v>2.2799999999999998</v>
-      </c>
-      <c r="J39" s="27">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="K39" s="27">
-        <v>1.86</v>
-      </c>
-      <c r="L39" s="27">
-        <v>1.92</v>
-      </c>
-      <c r="M39" s="27">
-        <v>2.46</v>
-      </c>
-      <c r="N39" s="27">
-        <v>1.99</v>
-      </c>
-      <c r="O39" s="27">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="D40" s="27">
-        <v>2.11</v>
-      </c>
-      <c r="E40" s="27">
-        <v>2.1</v>
-      </c>
-      <c r="F40" s="27">
-        <v>1.78</v>
-      </c>
-      <c r="G40" s="27">
-        <v>2.4</v>
-      </c>
-      <c r="H40" s="27">
-        <v>2.67</v>
-      </c>
-      <c r="I40" s="27">
-        <v>2.77</v>
-      </c>
-      <c r="J40" s="27">
-        <v>2.73</v>
-      </c>
-      <c r="K40" s="27">
-        <v>2.42</v>
-      </c>
-      <c r="L40" s="27">
-        <v>2.09</v>
-      </c>
-      <c r="M40" s="27">
-        <v>3.21</v>
-      </c>
-      <c r="N40" s="27">
-        <v>2.69</v>
-      </c>
-      <c r="O40" s="27">
-        <v>2.12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D41" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="27">
-        <v>2.73</v>
-      </c>
-      <c r="H41" s="27">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="I41" s="27">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="J41" s="27">
-        <v>2.14</v>
-      </c>
-      <c r="K41" s="27">
-        <v>2.16</v>
-      </c>
-      <c r="L41" s="27">
-        <v>2.27</v>
-      </c>
-      <c r="M41" s="27">
-        <v>2.67</v>
-      </c>
-      <c r="N41" s="27">
-        <v>2.58</v>
-      </c>
-      <c r="O41" s="27">
-        <v>3.33</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="27">
-        <v>4.8899999999999997</v>
-      </c>
-      <c r="H42" s="27">
-        <v>7.11</v>
-      </c>
-      <c r="I42" s="27">
-        <v>5.66</v>
-      </c>
-      <c r="J42" s="27">
-        <v>6.31</v>
-      </c>
-      <c r="K42" s="27">
-        <v>4.96</v>
-      </c>
-      <c r="L42" s="27">
-        <v>6.07</v>
-      </c>
-      <c r="M42" s="27">
-        <v>5.14</v>
-      </c>
-      <c r="N42" s="27">
-        <v>5.5</v>
-      </c>
-      <c r="O42" s="27">
-        <v>4.66</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="D43" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="27">
-        <v>2.77</v>
-      </c>
-      <c r="H43" s="27">
-        <v>2.8</v>
-      </c>
-      <c r="I43" s="27">
-        <v>2.04</v>
-      </c>
-      <c r="J43" s="27">
-        <v>2.31</v>
-      </c>
-      <c r="K43" s="27">
-        <v>2.4300000000000002</v>
-      </c>
-      <c r="L43" s="27">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="M43" s="27">
-        <v>2.72</v>
-      </c>
-      <c r="N43" s="27">
-        <v>2.44</v>
-      </c>
-      <c r="O43" s="27">
-        <v>2.39</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="27">
-        <v>12.71</v>
-      </c>
-      <c r="H44" s="27">
-        <v>15.95</v>
-      </c>
-      <c r="I44" s="27">
-        <v>12.84</v>
-      </c>
-      <c r="J44" s="27">
-        <v>13.72</v>
-      </c>
-      <c r="K44" s="27">
-        <v>12.03</v>
-      </c>
-      <c r="L44" s="27">
-        <v>13.72</v>
-      </c>
-      <c r="M44" s="27">
-        <v>14.04</v>
-      </c>
-      <c r="N44" s="27">
-        <v>13.42</v>
-      </c>
-      <c r="O44" s="27">
-        <v>12.97</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="E45" s="15"/>
-      <c r="F45" s="15"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="15"/>
-      <c r="I45" s="15"/>
-      <c r="J45" s="15"/>
-      <c r="K45" s="15"/>
-      <c r="L45" s="15"/>
-      <c r="M45" s="15"/>
-      <c r="N45" s="15"/>
-      <c r="O45" s="15"/>
-    </row>
-    <row r="46" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="23"/>
-      <c r="B46" s="23"/>
-      <c r="C46" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="D46" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E46" s="25"/>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25"/>
-      <c r="H46" s="25"/>
-      <c r="I46" s="25"/>
-      <c r="J46" s="25"/>
-      <c r="K46" s="25"/>
-      <c r="L46" s="25"/>
-      <c r="M46" s="25"/>
-      <c r="N46" s="25"/>
-      <c r="O46" s="25"/>
-    </row>
-    <row r="47" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="D47" s="28">
-        <v>89.7</v>
-      </c>
-      <c r="E47" s="28">
-        <v>73.599999999999994</v>
-      </c>
-      <c r="F47" s="28">
-        <v>43.3</v>
-      </c>
-      <c r="G47" s="28">
-        <v>63.5</v>
-      </c>
-      <c r="H47" s="28">
-        <v>20.8</v>
-      </c>
-      <c r="I47" s="28">
-        <v>80.900000000000006</v>
-      </c>
-      <c r="J47" s="28">
-        <v>33.4</v>
-      </c>
-      <c r="K47" s="28">
-        <v>26.5</v>
-      </c>
-      <c r="L47" s="28">
-        <v>27.6</v>
-      </c>
-      <c r="M47" s="28">
-        <v>21.6</v>
-      </c>
-      <c r="N47" s="28">
-        <v>35.6</v>
-      </c>
-      <c r="O47" s="28">
-        <v>29.1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="D48" s="26">
-        <v>20.5</v>
-      </c>
-      <c r="E48" s="26">
-        <v>-13.8</v>
-      </c>
-      <c r="F48" s="26">
-        <v>-1.2</v>
-      </c>
-      <c r="G48" s="26">
-        <v>-2.5</v>
-      </c>
-      <c r="H48" s="26">
-        <v>-5.4</v>
-      </c>
-      <c r="I48" s="26">
-        <v>4.8</v>
-      </c>
-      <c r="J48" s="26">
-        <v>7.7</v>
-      </c>
-      <c r="K48" s="26">
-        <v>-7.1</v>
-      </c>
-      <c r="L48" s="26">
-        <v>-4.7</v>
-      </c>
-      <c r="M48" s="26">
-        <v>14.4</v>
-      </c>
-      <c r="N48" s="26">
-        <v>5.4</v>
-      </c>
-      <c r="O48" s="26">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="26">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="J49" s="26">
-        <v>0.7</v>
-      </c>
-      <c r="K49" s="26">
-        <v>-0.2</v>
-      </c>
-      <c r="L49" s="26">
-        <v>-0.1</v>
-      </c>
-      <c r="M49" s="14"/>
-      <c r="N49" s="14"/>
-      <c r="O49" s="14"/>
-    </row>
-    <row r="50" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="D50" s="26">
-        <v>5.8</v>
-      </c>
-      <c r="E50" s="26">
-        <v>0.6</v>
-      </c>
-      <c r="F50" s="26">
-        <v>-6.4</v>
-      </c>
-      <c r="G50" s="26">
-        <v>0.3</v>
-      </c>
-      <c r="H50" s="26">
-        <v>-0.4</v>
-      </c>
-      <c r="I50" s="26">
-        <v>2.8</v>
-      </c>
-      <c r="J50" s="26">
-        <v>6.7</v>
-      </c>
-      <c r="K50" s="26">
-        <v>5.9</v>
-      </c>
-      <c r="L50" s="26">
-        <v>4.8</v>
-      </c>
-      <c r="M50" s="26">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="N50" s="26">
-        <v>24.8</v>
-      </c>
-      <c r="O50" s="26">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="D51" s="26">
-        <v>-74.5</v>
-      </c>
-      <c r="E51" s="26">
-        <v>45.5</v>
-      </c>
-      <c r="F51" s="26">
-        <v>-14.7</v>
-      </c>
-      <c r="G51" s="26">
-        <v>-14.7</v>
-      </c>
-      <c r="H51" s="26">
-        <v>57.4</v>
-      </c>
-      <c r="I51" s="26">
-        <v>-43.8</v>
-      </c>
-      <c r="J51" s="26">
-        <v>23.5</v>
-      </c>
-      <c r="K51" s="26">
-        <v>14.7</v>
-      </c>
-      <c r="L51" s="26">
-        <v>-18.7</v>
-      </c>
-      <c r="M51" s="14"/>
-      <c r="N51" s="26">
-        <v>-29.8</v>
-      </c>
-      <c r="O51" s="26">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="D52" s="26">
-        <v>-17.600000000000001</v>
-      </c>
-      <c r="E52" s="14"/>
-      <c r="F52" s="26">
-        <v>23.3</v>
-      </c>
-      <c r="G52" s="26">
-        <v>-12.4</v>
-      </c>
-      <c r="H52" s="26">
-        <v>-1.8</v>
-      </c>
-      <c r="I52" s="26">
-        <v>-5.5</v>
-      </c>
-      <c r="J52" s="26">
-        <v>-16.100000000000001</v>
-      </c>
-      <c r="K52" s="26">
-        <v>-22.1</v>
-      </c>
-      <c r="L52" s="26">
-        <v>8.9</v>
-      </c>
-      <c r="M52" s="26">
-        <v>-8.6</v>
-      </c>
-      <c r="N52" s="26">
-        <v>4.2</v>
-      </c>
-      <c r="O52" s="26">
-        <v>22.6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D53" s="26">
-        <v>6</v>
-      </c>
-      <c r="E53" s="26">
-        <v>-9.5</v>
-      </c>
-      <c r="F53" s="26">
-        <v>-13.3</v>
-      </c>
-      <c r="G53" s="26">
-        <v>0.2</v>
-      </c>
-      <c r="H53" s="26">
-        <v>-26</v>
-      </c>
-      <c r="I53" s="26">
-        <v>-6.5</v>
-      </c>
-      <c r="J53" s="26">
-        <v>-9.6999999999999993</v>
-      </c>
-      <c r="K53" s="26">
-        <v>7.7</v>
-      </c>
-      <c r="L53" s="26">
-        <v>11.6</v>
-      </c>
-      <c r="M53" s="14"/>
-      <c r="N53" s="26">
-        <v>2.8</v>
-      </c>
-      <c r="O53" s="26">
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="D54" s="26">
-        <v>-9.1</v>
-      </c>
-      <c r="E54" s="14"/>
-      <c r="F54" s="26">
-        <v>2.9</v>
-      </c>
-      <c r="G54" s="26">
-        <v>-6.5</v>
-      </c>
-      <c r="H54" s="26">
-        <v>-15.5</v>
-      </c>
-      <c r="I54" s="26">
-        <v>-13.3</v>
-      </c>
-      <c r="J54" s="26">
-        <v>-10.6</v>
-      </c>
-      <c r="K54" s="26">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="L54" s="26">
-        <v>1</v>
-      </c>
-      <c r="M54" s="26">
-        <v>-2.9</v>
-      </c>
-      <c r="N54" s="26">
-        <v>-3.5</v>
-      </c>
-      <c r="O54" s="26">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="D55" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E55" s="26">
-        <v>-13.7</v>
-      </c>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="14"/>
-      <c r="J55" s="14"/>
-      <c r="K55" s="14"/>
-      <c r="L55" s="14"/>
-      <c r="M55" s="14"/>
-      <c r="N55" s="14"/>
-      <c r="O55" s="14"/>
-    </row>
-    <row r="56" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="D56" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E56" s="26">
-        <v>-1.8</v>
-      </c>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="14"/>
-      <c r="J56" s="14"/>
-      <c r="K56" s="14"/>
-      <c r="L56" s="14"/>
-      <c r="M56" s="14"/>
-      <c r="N56" s="14"/>
-      <c r="O56" s="14"/>
-    </row>
-    <row r="57" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="D57" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E57" s="14"/>
-      <c r="F57" s="26">
-        <v>-1.5</v>
-      </c>
-      <c r="G57" s="26">
-        <v>-1.5</v>
-      </c>
-      <c r="H57" s="26">
-        <v>-1.6</v>
-      </c>
-      <c r="I57" s="14"/>
-      <c r="J57" s="14"/>
-      <c r="K57" s="14"/>
-      <c r="L57" s="14"/>
-      <c r="M57" s="26">
-        <v>-1.2</v>
-      </c>
-      <c r="N57" s="14"/>
-      <c r="O57" s="14"/>
-    </row>
-    <row r="58" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D58" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="14"/>
-      <c r="J58" s="14"/>
-      <c r="K58" s="14"/>
-      <c r="L58" s="14"/>
-      <c r="M58" s="26">
-        <v>-3.6</v>
-      </c>
-      <c r="N58" s="26">
-        <v>0.7</v>
-      </c>
-      <c r="O58" s="26">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="D59" s="28">
-        <v>20.8</v>
-      </c>
-      <c r="E59" s="28">
-        <v>80.900000000000006</v>
-      </c>
-      <c r="F59" s="28">
-        <v>32.5</v>
-      </c>
-      <c r="G59" s="28">
-        <v>26.5</v>
-      </c>
-      <c r="H59" s="28">
-        <v>27.6</v>
-      </c>
-      <c r="I59" s="28">
-        <v>21.6</v>
-      </c>
-      <c r="J59" s="28">
-        <v>35.6</v>
-      </c>
-      <c r="K59" s="28">
-        <v>29.1</v>
-      </c>
-      <c r="L59" s="28">
-        <v>30</v>
-      </c>
-      <c r="M59" s="28">
-        <v>29</v>
-      </c>
-      <c r="N59" s="28">
-        <v>40.200000000000003</v>
-      </c>
-      <c r="O59" s="28">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="6"/>
-      <c r="B60" s="6"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="E60" s="15"/>
-      <c r="F60" s="15"/>
-      <c r="G60" s="15"/>
-      <c r="H60" s="15"/>
-      <c r="I60" s="15"/>
-      <c r="J60" s="15"/>
-      <c r="K60" s="15"/>
-      <c r="L60" s="15"/>
-      <c r="M60" s="15"/>
-      <c r="N60" s="15"/>
-      <c r="O60" s="15"/>
-    </row>
-    <row r="61" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="23"/>
-      <c r="B61" s="23"/>
-      <c r="C61" s="24" t="s">
-        <v>266</v>
-      </c>
-      <c r="D61" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E61" s="25"/>
-      <c r="F61" s="25"/>
-      <c r="G61" s="25"/>
-      <c r="H61" s="25"/>
-      <c r="I61" s="25"/>
-      <c r="J61" s="25"/>
-      <c r="K61" s="25"/>
-      <c r="L61" s="25"/>
-      <c r="M61" s="25"/>
-      <c r="N61" s="25"/>
-      <c r="O61" s="25"/>
-    </row>
-    <row r="62" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="D62" s="10">
-        <v>367</v>
-      </c>
-      <c r="E62" s="10">
-        <v>486</v>
-      </c>
-      <c r="F62" s="10">
-        <v>727</v>
-      </c>
-      <c r="G62" s="10">
-        <v>518</v>
-      </c>
-      <c r="H62" s="10">
-        <v>15</v>
-      </c>
-      <c r="I62" s="10">
-        <v>1245</v>
-      </c>
-      <c r="J62" s="10">
-        <v>615</v>
-      </c>
-      <c r="K62" s="10">
-        <v>629</v>
-      </c>
-      <c r="L62" s="10">
-        <v>914</v>
-      </c>
-      <c r="M62" s="10">
-        <v>1599</v>
-      </c>
-      <c r="N62" s="10">
-        <v>1150</v>
-      </c>
-      <c r="O62" s="10">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D63" s="8">
-        <v>-186</v>
-      </c>
-      <c r="E63" s="8">
-        <v>205</v>
-      </c>
-      <c r="F63" s="8">
-        <v>343</v>
-      </c>
-      <c r="G63" s="8">
-        <v>-3</v>
-      </c>
-      <c r="H63" s="8">
-        <v>647</v>
-      </c>
-      <c r="I63" s="8">
-        <v>156</v>
-      </c>
-      <c r="J63" s="8">
-        <v>173</v>
-      </c>
-      <c r="K63" s="8">
-        <v>-156</v>
-      </c>
-      <c r="L63" s="8">
-        <v>-297</v>
-      </c>
-      <c r="M63" s="8">
-        <v>-16</v>
-      </c>
-      <c r="N63" s="8">
-        <v>-122</v>
-      </c>
-      <c r="O63" s="8">
-        <v>-12</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D64" s="8">
-        <v>-210</v>
-      </c>
-      <c r="E64" s="8">
-        <v>302</v>
-      </c>
-      <c r="F64" s="8">
-        <v>-49</v>
-      </c>
-      <c r="G64" s="8">
-        <v>154</v>
-      </c>
-      <c r="H64" s="8">
-        <v>520</v>
-      </c>
-      <c r="I64" s="8">
-        <v>207</v>
-      </c>
-      <c r="J64" s="8">
-        <v>53</v>
-      </c>
-      <c r="K64" s="8">
-        <v>61</v>
-      </c>
-      <c r="L64" s="8">
-        <v>95</v>
-      </c>
-      <c r="M64" s="8">
-        <v>-537</v>
-      </c>
-      <c r="N64" s="8">
-        <v>33</v>
-      </c>
-      <c r="O64" s="8">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="D65" s="8">
-        <v>3</v>
-      </c>
-      <c r="E65" s="8">
-        <v>237</v>
-      </c>
-      <c r="F65" s="8">
-        <v>-283</v>
-      </c>
-      <c r="G65" s="8">
-        <v>99</v>
-      </c>
-      <c r="H65" s="8">
-        <v>27</v>
-      </c>
-      <c r="I65" s="8">
-        <v>158</v>
-      </c>
-      <c r="J65" s="8">
-        <v>272</v>
-      </c>
-      <c r="K65" s="8">
-        <v>312</v>
-      </c>
-      <c r="L65" s="8">
-        <v>-108</v>
-      </c>
-      <c r="M65" s="8">
-        <v>112</v>
-      </c>
-      <c r="N65" s="8">
-        <v>-47</v>
-      </c>
-      <c r="O65" s="8">
-        <v>-122</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="D66" s="8">
-        <v>19</v>
-      </c>
-      <c r="E66" s="8">
-        <v>24</v>
-      </c>
-      <c r="F66" s="8">
-        <v>5</v>
-      </c>
-      <c r="G66" s="8">
-        <v>7</v>
-      </c>
-      <c r="H66" s="8">
-        <v>2</v>
-      </c>
-      <c r="I66" s="8">
-        <v>5</v>
-      </c>
-      <c r="J66" s="8">
-        <v>-9</v>
-      </c>
-      <c r="K66" s="8">
-        <v>-12</v>
-      </c>
-      <c r="L66" s="8">
-        <v>10</v>
-      </c>
-      <c r="M66" s="8">
-        <v>-16</v>
-      </c>
-      <c r="N66" s="8">
-        <v>-3</v>
-      </c>
-      <c r="O66" s="8">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="D67" s="8">
-        <v>-5</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-26</v>
-      </c>
-      <c r="F67" s="8">
-        <v>6</v>
-      </c>
-      <c r="G67" s="8"/>
-      <c r="H67" s="8"/>
-      <c r="I67" s="8"/>
-      <c r="J67" s="8"/>
-      <c r="K67" s="8"/>
-      <c r="L67" s="8"/>
-      <c r="M67" s="8"/>
-      <c r="N67" s="8"/>
-      <c r="O67" s="8"/>
-    </row>
-    <row r="68" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="8">
-        <v>28</v>
-      </c>
-      <c r="H68" s="8">
-        <v>-28</v>
-      </c>
-      <c r="I68" s="8">
-        <v>-4</v>
-      </c>
-      <c r="J68" s="8">
-        <v>9</v>
-      </c>
-      <c r="K68" s="8">
-        <v>-20</v>
-      </c>
-      <c r="L68" s="8">
-        <v>12</v>
-      </c>
-      <c r="M68" s="8">
-        <v>-21</v>
-      </c>
-      <c r="N68" s="8">
-        <v>23</v>
-      </c>
-      <c r="O68" s="8">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="D69" s="8">
-        <v>26</v>
-      </c>
-      <c r="E69" s="8">
-        <v>17</v>
-      </c>
-      <c r="F69" s="8">
-        <v>-132</v>
-      </c>
-      <c r="G69" s="8">
-        <v>-174</v>
-      </c>
-      <c r="H69" s="8">
-        <v>-269</v>
-      </c>
-      <c r="I69" s="8">
-        <v>-168</v>
-      </c>
-      <c r="J69" s="8">
-        <v>37</v>
-      </c>
-      <c r="K69" s="8">
-        <v>132</v>
-      </c>
-      <c r="L69" s="8">
-        <v>62</v>
-      </c>
-      <c r="M69" s="8">
-        <v>112</v>
-      </c>
-      <c r="N69" s="8">
-        <v>284</v>
-      </c>
-      <c r="O69" s="8">
-        <v>-260</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="D70" s="10">
-        <v>15</v>
-      </c>
-      <c r="E70" s="10">
-        <v>1245</v>
-      </c>
-      <c r="F70" s="10">
-        <v>615</v>
-      </c>
-      <c r="G70" s="10">
-        <v>629</v>
-      </c>
-      <c r="H70" s="10">
-        <v>914</v>
-      </c>
-      <c r="I70" s="10">
-        <v>1599</v>
-      </c>
-      <c r="J70" s="10">
-        <v>1150</v>
-      </c>
-      <c r="K70" s="10">
-        <v>946</v>
-      </c>
-      <c r="L70" s="10">
-        <v>688</v>
-      </c>
-      <c r="M70" s="10">
-        <v>1234</v>
-      </c>
-      <c r="N70" s="10">
-        <v>1318</v>
-      </c>
-      <c r="O70" s="10">
-        <v>1114</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB012AFB-0069-B049-2769-3A59A928ED4A}">
-  <dimension ref="A1:O53"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="25" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="66.6640625" style="13" customWidth="1" collapsed="1"/>
-    <col min="4" max="15" width="25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
@@ -10307,17 +7377,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EF311EB-4BB9-AB9C-DDE4-417EAC7E50BE}">
   <dimension ref="A1:F53"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.36328125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="25" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="66.6640625" style="13" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="66.6328125" style="13" customWidth="1" collapsed="1"/>
     <col min="4" max="6" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10337,7 +7407,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
@@ -10353,7 +7423,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
@@ -11295,6 +8365,929 @@
       </c>
       <c r="F53" s="10">
         <v>1015</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C7BD195-77B1-508A-D804-78471E850F8F}">
+  <dimension ref="A1:F50"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.36328125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="25" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="3" max="3" width="66.6328125" style="13" customWidth="1" collapsed="1"/>
+    <col min="4" max="6" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+    </row>
+    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+    </row>
+    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="26">
+        <v>294.89999999999998</v>
+      </c>
+      <c r="F6" s="26">
+        <v>240.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="26">
+        <v>11.8</v>
+      </c>
+      <c r="F7" s="26">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="D8" s="26">
+        <v>276.10000000000002</v>
+      </c>
+      <c r="E8" s="26">
+        <v>306.7</v>
+      </c>
+      <c r="F8" s="26">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="26">
+        <v>284.5</v>
+      </c>
+      <c r="E9" s="26">
+        <v>312.89999999999998</v>
+      </c>
+      <c r="F9" s="26">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="D10" s="26">
+        <v>5.2</v>
+      </c>
+      <c r="E10" s="26">
+        <v>4.3</v>
+      </c>
+      <c r="F10" s="26">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="D11" s="26">
+        <v>-13.6</v>
+      </c>
+      <c r="E11" s="26">
+        <v>-10.5</v>
+      </c>
+      <c r="F11" s="26">
+        <v>-6.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="D12" s="26">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="E12" s="26">
+        <v>16.7</v>
+      </c>
+      <c r="F12" s="26">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" s="26">
+        <v>-94</v>
+      </c>
+      <c r="E13" s="26">
+        <v>22</v>
+      </c>
+      <c r="F13" s="26">
+        <v>-18.100000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="26">
+        <v>13</v>
+      </c>
+      <c r="F14" s="26">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="26">
+        <v>1.9</v>
+      </c>
+      <c r="E15" s="26">
+        <v>2.8</v>
+      </c>
+      <c r="F15" s="26">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="D16" s="26">
+        <v>60.1</v>
+      </c>
+      <c r="E16" s="26">
+        <v>-65</v>
+      </c>
+      <c r="F16" s="26">
+        <v>-20.399999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="D17" s="26">
+        <v>-9.3000000000000007</v>
+      </c>
+      <c r="E17" s="26">
+        <v>-44.4</v>
+      </c>
+      <c r="F17" s="26">
+        <v>-41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="D18" s="26">
+        <v>-10.4</v>
+      </c>
+      <c r="E18" s="26">
+        <v>-46.3</v>
+      </c>
+      <c r="F18" s="26">
+        <v>-100.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="D19" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="E19" s="26">
+        <v>2</v>
+      </c>
+      <c r="F19" s="26">
+        <v>62.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D20" s="26">
+        <v>1.9</v>
+      </c>
+      <c r="E20" s="26">
+        <v>2</v>
+      </c>
+      <c r="F20" s="26">
+        <v>63.1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+    </row>
+    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+    </row>
+    <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+    </row>
+    <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="26">
+        <v>306.7</v>
+      </c>
+      <c r="F24" s="26">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="26">
+        <v>312.89999999999998</v>
+      </c>
+      <c r="F25" s="26">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="26">
+        <v>4.3</v>
+      </c>
+      <c r="F26" s="26">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="26">
+        <v>-10.5</v>
+      </c>
+      <c r="F27" s="26">
+        <v>-6.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="26">
+        <v>2.8</v>
+      </c>
+      <c r="F28" s="26">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="26">
+        <v>-13.3</v>
+      </c>
+      <c r="F29" s="26">
+        <v>-7.8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="26">
+        <v>-9.4</v>
+      </c>
+      <c r="F30" s="26">
+        <v>-5.2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="D31" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="26">
+        <v>-17</v>
+      </c>
+      <c r="F31" s="26">
+        <v>-11.9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="D32" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="26">
+        <v>-17.899999999999999</v>
+      </c>
+      <c r="F32" s="26">
+        <v>-17.100000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="26">
+        <v>0.9</v>
+      </c>
+      <c r="F33" s="26">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D34" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" s="26">
+        <v>1</v>
+      </c>
+      <c r="F34" s="26">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+    </row>
+    <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="D36" s="8">
+        <v>11876</v>
+      </c>
+      <c r="E36" s="8">
+        <v>12322</v>
+      </c>
+      <c r="F36" s="8">
+        <v>10306</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="D37" s="8">
+        <v>13497</v>
+      </c>
+      <c r="E37" s="8">
+        <v>11377</v>
+      </c>
+      <c r="F37" s="8">
+        <v>10164</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="D38" s="8">
+        <v>13448</v>
+      </c>
+      <c r="E38" s="8">
+        <v>11235</v>
+      </c>
+      <c r="F38" s="8">
+        <v>10912</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="D39" s="27">
+        <v>18.73</v>
+      </c>
+      <c r="E39" s="27">
+        <v>24.19</v>
+      </c>
+      <c r="F39" s="27">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="D40" s="27">
+        <v>19.690000000000001</v>
+      </c>
+      <c r="E40" s="27">
+        <v>25.39</v>
+      </c>
+      <c r="F40" s="27">
+        <v>22.05</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+    </row>
+    <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+    </row>
+    <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+    </row>
+    <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="D44" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" s="26">
+        <v>-22.6</v>
+      </c>
+      <c r="F44" s="26">
+        <v>-9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="D45" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" s="26">
+        <v>-23</v>
+      </c>
+      <c r="F45" s="26">
+        <v>-16.7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="D46" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" s="26">
+        <v>-23.9</v>
+      </c>
+      <c r="F46" s="26">
+        <v>-71</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="D47" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47" s="26">
+        <v>1</v>
+      </c>
+      <c r="F47" s="26">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D48" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48" s="26">
+        <v>1</v>
+      </c>
+      <c r="F48" s="26">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+    </row>
+    <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="8">
+        <v>1522</v>
+      </c>
+      <c r="F50" s="8">
+        <v>11303</v>
       </c>
     </row>
   </sheetData>
@@ -11303,17 +9296,17 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C7BD195-77B1-508A-D804-78471E850F8F}">
-  <dimension ref="A1:F50"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{696A46DF-C2E1-5DF4-52C8-FDF6064D6637}">
+  <dimension ref="A1:O70"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.36328125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="25" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="66.6640625" style="13" customWidth="1" collapsed="1"/>
-    <col min="4" max="6" width="25" customWidth="1"/>
+    <col min="3" max="3" width="66.6328125" style="13" customWidth="1" collapsed="1"/>
+    <col min="4" max="15" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -11323,972 +9316,49 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="23"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-    </row>
-    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-    </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="26">
-        <v>294.89999999999998</v>
-      </c>
-      <c r="F6" s="26">
-        <v>240.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="26">
-        <v>11.8</v>
-      </c>
-      <c r="F7" s="26">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="D8" s="26">
-        <v>276.10000000000002</v>
-      </c>
-      <c r="E8" s="26">
-        <v>306.7</v>
-      </c>
-      <c r="F8" s="26">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D9" s="26">
-        <v>284.5</v>
-      </c>
-      <c r="E9" s="26">
-        <v>312.89999999999998</v>
-      </c>
-      <c r="F9" s="26">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="D10" s="26">
-        <v>5.2</v>
-      </c>
-      <c r="E10" s="26">
-        <v>4.3</v>
-      </c>
-      <c r="F10" s="26">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="D11" s="26">
-        <v>-13.6</v>
-      </c>
-      <c r="E11" s="26">
-        <v>-10.5</v>
-      </c>
-      <c r="F11" s="26">
-        <v>-6.4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="D12" s="26">
-        <v>18.399999999999999</v>
-      </c>
-      <c r="E12" s="26">
-        <v>16.7</v>
-      </c>
-      <c r="F12" s="26">
-        <v>9.3000000000000007</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" s="26">
-        <v>-94</v>
-      </c>
-      <c r="E13" s="26">
-        <v>22</v>
-      </c>
-      <c r="F13" s="26">
-        <v>-18.100000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="26">
-        <v>13</v>
-      </c>
-      <c r="F14" s="26">
-        <v>21.1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" s="26">
-        <v>1.9</v>
-      </c>
-      <c r="E15" s="26">
-        <v>2.8</v>
-      </c>
-      <c r="F15" s="26">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="D16" s="26">
-        <v>60.1</v>
-      </c>
-      <c r="E16" s="26">
-        <v>-65</v>
-      </c>
-      <c r="F16" s="26">
-        <v>-20.399999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="D17" s="26">
-        <v>-9.3000000000000007</v>
-      </c>
-      <c r="E17" s="26">
-        <v>-44.4</v>
-      </c>
-      <c r="F17" s="26">
-        <v>-41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="D18" s="26">
-        <v>-10.4</v>
-      </c>
-      <c r="E18" s="26">
-        <v>-46.3</v>
-      </c>
-      <c r="F18" s="26">
-        <v>-100.7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="D19" s="26">
-        <v>1.8</v>
-      </c>
-      <c r="E19" s="26">
-        <v>2</v>
-      </c>
-      <c r="F19" s="26">
-        <v>62.3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="D20" s="26">
-        <v>1.9</v>
-      </c>
-      <c r="E20" s="26">
-        <v>2</v>
-      </c>
-      <c r="F20" s="26">
-        <v>63.1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-    </row>
-    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-    </row>
-    <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="D24" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" s="26">
-        <v>306.7</v>
-      </c>
-      <c r="F24" s="26">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" s="26">
-        <v>312.89999999999998</v>
-      </c>
-      <c r="F25" s="26">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="26">
-        <v>4.3</v>
-      </c>
-      <c r="F26" s="26">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" s="26">
-        <v>-10.5</v>
-      </c>
-      <c r="F27" s="26">
-        <v>-6.4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D28" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" s="26">
-        <v>2.8</v>
-      </c>
-      <c r="F28" s="26">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="D29" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E29" s="26">
-        <v>-13.3</v>
-      </c>
-      <c r="F29" s="26">
-        <v>-7.8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" s="26">
-        <v>-9.4</v>
-      </c>
-      <c r="F30" s="26">
-        <v>-5.2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="D31" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E31" s="26">
-        <v>-17</v>
-      </c>
-      <c r="F31" s="26">
-        <v>-11.9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="D32" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E32" s="26">
-        <v>-17.899999999999999</v>
-      </c>
-      <c r="F32" s="26">
-        <v>-17.100000000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="D33" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E33" s="26">
-        <v>0.9</v>
-      </c>
-      <c r="F33" s="26">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="D34" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E34" s="26">
-        <v>1</v>
-      </c>
-      <c r="F34" s="26">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-    </row>
-    <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="D36" s="8">
-        <v>11876</v>
-      </c>
-      <c r="E36" s="8">
-        <v>12322</v>
-      </c>
-      <c r="F36" s="8">
-        <v>10306</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="D37" s="8">
-        <v>13497</v>
-      </c>
-      <c r="E37" s="8">
-        <v>11377</v>
-      </c>
-      <c r="F37" s="8">
-        <v>10164</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="D38" s="8">
-        <v>13448</v>
-      </c>
-      <c r="E38" s="8">
-        <v>11235</v>
-      </c>
-      <c r="F38" s="8">
-        <v>10912</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="D39" s="27">
-        <v>18.73</v>
-      </c>
-      <c r="E39" s="27">
-        <v>24.19</v>
-      </c>
-      <c r="F39" s="27">
-        <v>21.3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="D40" s="27">
-        <v>19.690000000000001</v>
-      </c>
-      <c r="E40" s="27">
-        <v>25.39</v>
-      </c>
-      <c r="F40" s="27">
-        <v>22.05</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-    </row>
-    <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-    </row>
-    <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-    </row>
-    <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="D44" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E44" s="26">
-        <v>-22.6</v>
-      </c>
-      <c r="F44" s="26">
-        <v>-9.8000000000000007</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="D45" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E45" s="26">
-        <v>-23</v>
-      </c>
-      <c r="F45" s="26">
-        <v>-16.7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="D46" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E46" s="26">
-        <v>-23.9</v>
-      </c>
-      <c r="F46" s="26">
-        <v>-71</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="D47" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E47" s="26">
-        <v>1</v>
-      </c>
-      <c r="F47" s="26">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="D48" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E48" s="26">
-        <v>1</v>
-      </c>
-      <c r="F48" s="26">
-        <v>57.8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-    </row>
-    <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>313</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E50" s="8">
-        <v>1522</v>
-      </c>
-      <c r="F50" s="8">
-        <v>11303</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9117E93F-4FAC-042A-B07E-6BCC9A0DDCF5}">
-  <dimension ref="A1:O49"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="25" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="66.6640625" style="13" customWidth="1" collapsed="1"/>
-    <col min="4" max="15" width="25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
         <v>62</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -12325,7 +9395,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
@@ -12418,6 +9488,2949 @@
         <v>150</v>
       </c>
       <c r="C6" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="D6" s="26">
+        <v>58.5</v>
+      </c>
+      <c r="E6" s="26">
+        <v>55.6</v>
+      </c>
+      <c r="F6" s="26">
+        <v>67.7</v>
+      </c>
+      <c r="G6" s="26">
+        <v>66.8</v>
+      </c>
+      <c r="H6" s="26">
+        <v>56.4</v>
+      </c>
+      <c r="I6" s="26">
+        <v>52.8</v>
+      </c>
+      <c r="J6" s="26">
+        <v>58.3</v>
+      </c>
+      <c r="K6" s="26">
+        <v>50.7</v>
+      </c>
+      <c r="L6" s="26">
+        <v>70</v>
+      </c>
+      <c r="M6" s="26">
+        <v>53.5</v>
+      </c>
+      <c r="N6" s="26">
+        <v>87.3</v>
+      </c>
+      <c r="O6" s="26">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="D7" s="26">
+        <v>73.3</v>
+      </c>
+      <c r="E7" s="26">
+        <v>41.5</v>
+      </c>
+      <c r="F7" s="26">
+        <v>49</v>
+      </c>
+      <c r="G7" s="26">
+        <v>52.7</v>
+      </c>
+      <c r="H7" s="26">
+        <v>52.4</v>
+      </c>
+      <c r="I7" s="26">
+        <v>32.9</v>
+      </c>
+      <c r="J7" s="26">
+        <v>46</v>
+      </c>
+      <c r="K7" s="26">
+        <v>49.7</v>
+      </c>
+      <c r="L7" s="26">
+        <v>48.7</v>
+      </c>
+      <c r="M7" s="26">
+        <v>44.4</v>
+      </c>
+      <c r="N7" s="26">
+        <v>47.8</v>
+      </c>
+      <c r="O7" s="26">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D8" s="26">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E8" s="26">
+        <v>1.9</v>
+      </c>
+      <c r="F8" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="G8" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="H8" s="26">
+        <v>2.1</v>
+      </c>
+      <c r="I8" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="J8" s="26">
+        <v>2</v>
+      </c>
+      <c r="K8" s="26">
+        <v>2.1</v>
+      </c>
+      <c r="L8" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="M8" s="26">
+        <v>1.9</v>
+      </c>
+      <c r="N8" s="26">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="O8" s="26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="D9" s="26">
+        <v>134.1</v>
+      </c>
+      <c r="E9" s="26">
+        <v>99</v>
+      </c>
+      <c r="F9" s="26">
+        <v>118.2</v>
+      </c>
+      <c r="G9" s="26">
+        <v>121.2</v>
+      </c>
+      <c r="H9" s="26">
+        <v>110.9</v>
+      </c>
+      <c r="I9" s="26">
+        <v>87.5</v>
+      </c>
+      <c r="J9" s="26">
+        <v>106.3</v>
+      </c>
+      <c r="K9" s="26">
+        <v>102.5</v>
+      </c>
+      <c r="L9" s="26">
+        <v>120.5</v>
+      </c>
+      <c r="M9" s="26">
+        <v>99.8</v>
+      </c>
+      <c r="N9" s="26">
+        <v>137.4</v>
+      </c>
+      <c r="O9" s="26">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="26">
+        <v>58.6</v>
+      </c>
+      <c r="E10" s="26">
+        <v>69.8</v>
+      </c>
+      <c r="F10" s="26">
+        <v>70.7</v>
+      </c>
+      <c r="G10" s="26">
+        <v>69.8</v>
+      </c>
+      <c r="H10" s="26">
+        <v>84.6</v>
+      </c>
+      <c r="I10" s="26">
+        <v>76.3</v>
+      </c>
+      <c r="J10" s="26">
+        <v>80.400000000000006</v>
+      </c>
+      <c r="K10" s="26">
+        <v>62.1</v>
+      </c>
+      <c r="L10" s="26">
+        <v>73</v>
+      </c>
+      <c r="M10" s="26">
+        <v>63.4</v>
+      </c>
+      <c r="N10" s="26">
+        <v>80.599999999999994</v>
+      </c>
+      <c r="O10" s="26">
+        <v>89.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="D11" s="26">
+        <v>23.5</v>
+      </c>
+      <c r="E11" s="26">
+        <v>26.5</v>
+      </c>
+      <c r="F11" s="26">
+        <v>13.5</v>
+      </c>
+      <c r="G11" s="26">
+        <v>15.8</v>
+      </c>
+      <c r="H11" s="26">
+        <v>17.3</v>
+      </c>
+      <c r="I11" s="26">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="J11" s="26">
+        <v>21.5</v>
+      </c>
+      <c r="K11" s="26">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="L11" s="26">
+        <v>18.3</v>
+      </c>
+      <c r="M11" s="26">
+        <v>14.1</v>
+      </c>
+      <c r="N11" s="26">
+        <v>19</v>
+      </c>
+      <c r="O11" s="26">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="26">
+        <v>52</v>
+      </c>
+      <c r="E12" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="F12" s="26">
+        <v>34</v>
+      </c>
+      <c r="G12" s="26">
+        <v>35.6</v>
+      </c>
+      <c r="H12" s="26">
+        <v>9</v>
+      </c>
+      <c r="I12" s="26">
+        <v>-8.6999999999999993</v>
+      </c>
+      <c r="J12" s="26">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="K12" s="26">
+        <v>22.5</v>
+      </c>
+      <c r="L12" s="26">
+        <v>29.2</v>
+      </c>
+      <c r="M12" s="26">
+        <v>22.3</v>
+      </c>
+      <c r="N12" s="26">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="O12" s="26">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" s="26">
+        <v>45.6</v>
+      </c>
+      <c r="E13" s="26">
+        <v>-3.4</v>
+      </c>
+      <c r="F13" s="26">
+        <v>28.2</v>
+      </c>
+      <c r="G13" s="26">
+        <v>29.7</v>
+      </c>
+      <c r="H13" s="26">
+        <v>6.9</v>
+      </c>
+      <c r="I13" s="26">
+        <v>-12.6</v>
+      </c>
+      <c r="J13" s="26">
+        <v>-0.8</v>
+      </c>
+      <c r="K13" s="26">
+        <v>17.5</v>
+      </c>
+      <c r="L13" s="26">
+        <v>23.6</v>
+      </c>
+      <c r="M13" s="26">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="N13" s="26">
+        <v>29.4</v>
+      </c>
+      <c r="O13" s="26">
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D14" s="26">
+        <v>20.8</v>
+      </c>
+      <c r="E14" s="26">
+        <v>80.900000000000006</v>
+      </c>
+      <c r="F14" s="26">
+        <v>33.4</v>
+      </c>
+      <c r="G14" s="26">
+        <v>26.5</v>
+      </c>
+      <c r="H14" s="26">
+        <v>27.6</v>
+      </c>
+      <c r="I14" s="26">
+        <v>21.6</v>
+      </c>
+      <c r="J14" s="26">
+        <v>35.6</v>
+      </c>
+      <c r="K14" s="26">
+        <v>29.1</v>
+      </c>
+      <c r="L14" s="26">
+        <v>30</v>
+      </c>
+      <c r="M14" s="26">
+        <v>29</v>
+      </c>
+      <c r="N14" s="26">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="O14" s="26">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="D15" s="26">
+        <v>6.4</v>
+      </c>
+      <c r="E15" s="26">
+        <v>57.5</v>
+      </c>
+      <c r="F15" s="26">
+        <v>20.9</v>
+      </c>
+      <c r="G15" s="26">
+        <v>15.6</v>
+      </c>
+      <c r="H15" s="26">
+        <v>24.6</v>
+      </c>
+      <c r="I15" s="26">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J15" s="26">
+        <v>25.2</v>
+      </c>
+      <c r="K15" s="26">
+        <v>14.1</v>
+      </c>
+      <c r="L15" s="26">
+        <v>24.1</v>
+      </c>
+      <c r="M15" s="26">
+        <v>13.5</v>
+      </c>
+      <c r="N15" s="26">
+        <v>15.6</v>
+      </c>
+      <c r="O15" s="26">
+        <v>65.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="D16" s="26">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="E16" s="26">
+        <v>18.3</v>
+      </c>
+      <c r="F16" s="26">
+        <v>6.6</v>
+      </c>
+      <c r="G16" s="26">
+        <v>14.6</v>
+      </c>
+      <c r="H16" s="26">
+        <v>4.3</v>
+      </c>
+      <c r="I16" s="26">
+        <v>11.9</v>
+      </c>
+      <c r="J16" s="26">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="K16" s="26">
+        <v>36.6</v>
+      </c>
+      <c r="L16" s="26">
+        <v>0.8</v>
+      </c>
+      <c r="M16" s="26">
+        <v>18.8</v>
+      </c>
+      <c r="N16" s="26">
+        <v>27.2</v>
+      </c>
+      <c r="O16" s="26">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="D17" s="26">
+        <v>13.4</v>
+      </c>
+      <c r="E17" s="26">
+        <v>20.9</v>
+      </c>
+      <c r="F17" s="26">
+        <v>10.4</v>
+      </c>
+      <c r="G17" s="26">
+        <v>10</v>
+      </c>
+      <c r="H17" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="I17" s="26">
+        <v>13.3</v>
+      </c>
+      <c r="J17" s="26">
+        <v>12.5</v>
+      </c>
+      <c r="K17" s="26">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="L17" s="26">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="M17" s="26">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="N17" s="26">
+        <v>24.7</v>
+      </c>
+      <c r="O17" s="26">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D18" s="26">
+        <v>12.5</v>
+      </c>
+      <c r="E18" s="26">
+        <v>20.3</v>
+      </c>
+      <c r="F18" s="26">
+        <v>10.4</v>
+      </c>
+      <c r="G18" s="26">
+        <v>9.9</v>
+      </c>
+      <c r="H18" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="I18" s="26">
+        <v>13.3</v>
+      </c>
+      <c r="J18" s="26">
+        <v>12.5</v>
+      </c>
+      <c r="K18" s="26">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="L18" s="26">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="M18" s="26">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="N18" s="26">
+        <v>24.7</v>
+      </c>
+      <c r="O18" s="26">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D19" s="26">
+        <v>0.9</v>
+      </c>
+      <c r="E19" s="26">
+        <v>0.6</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="H19" s="14">
+        <v>0</v>
+      </c>
+      <c r="I19" s="14">
+        <v>0</v>
+      </c>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="26"/>
+    </row>
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+    </row>
+    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="D21" s="8">
+        <v>10651</v>
+      </c>
+      <c r="E21" s="8">
+        <v>11602</v>
+      </c>
+      <c r="F21" s="8">
+        <v>11924</v>
+      </c>
+      <c r="G21" s="8">
+        <v>10185</v>
+      </c>
+      <c r="H21" s="8">
+        <v>11321</v>
+      </c>
+      <c r="I21" s="8">
+        <v>12939</v>
+      </c>
+      <c r="J21" s="8">
+        <v>13357</v>
+      </c>
+      <c r="K21" s="8">
+        <v>12397</v>
+      </c>
+      <c r="L21" s="8">
+        <v>12332</v>
+      </c>
+      <c r="M21" s="8">
+        <v>12314</v>
+      </c>
+      <c r="N21" s="8">
+        <v>11801</v>
+      </c>
+      <c r="O21" s="8">
+        <v>9622</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="D22" s="8">
+        <v>4992</v>
+      </c>
+      <c r="E22" s="8">
+        <v>4556</v>
+      </c>
+      <c r="F22" s="8">
+        <v>5294</v>
+      </c>
+      <c r="G22" s="8">
+        <v>4578</v>
+      </c>
+      <c r="H22" s="8">
+        <v>3869</v>
+      </c>
+      <c r="I22" s="8">
+        <v>5252</v>
+      </c>
+      <c r="J22" s="8">
+        <v>5900</v>
+      </c>
+      <c r="K22" s="8">
+        <v>6256</v>
+      </c>
+      <c r="L22" s="8">
+        <v>5414</v>
+      </c>
+      <c r="M22" s="8">
+        <v>5605</v>
+      </c>
+      <c r="N22" s="8">
+        <v>5066</v>
+      </c>
+      <c r="O22" s="8">
+        <v>5844</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="D23" s="8">
+        <v>5251</v>
+      </c>
+      <c r="E23" s="8">
+        <v>5055</v>
+      </c>
+      <c r="F23" s="8">
+        <v>5538</v>
+      </c>
+      <c r="G23" s="8">
+        <v>5504</v>
+      </c>
+      <c r="H23" s="8">
+        <v>4705</v>
+      </c>
+      <c r="I23" s="8">
+        <v>5595</v>
+      </c>
+      <c r="J23" s="8">
+        <v>5605</v>
+      </c>
+      <c r="K23" s="8">
+        <v>5775</v>
+      </c>
+      <c r="L23" s="8">
+        <v>5162</v>
+      </c>
+      <c r="M23" s="8">
+        <v>5325</v>
+      </c>
+      <c r="N23" s="8">
+        <v>5553</v>
+      </c>
+      <c r="O23" s="8">
+        <v>5423</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="D24" s="27">
+        <v>0.35</v>
+      </c>
+      <c r="E24" s="27">
+        <v>0.39</v>
+      </c>
+      <c r="F24" s="27">
+        <v>0.47</v>
+      </c>
+      <c r="G24" s="27">
+        <v>0.47</v>
+      </c>
+      <c r="H24" s="27">
+        <v>0.34</v>
+      </c>
+      <c r="I24" s="27">
+        <v>0.38</v>
+      </c>
+      <c r="J24" s="27">
+        <v>0.35</v>
+      </c>
+      <c r="K24" s="27">
+        <v>0.35</v>
+      </c>
+      <c r="L24" s="27">
+        <v>0.46</v>
+      </c>
+      <c r="M24" s="27">
+        <v>0.36</v>
+      </c>
+      <c r="N24" s="27">
+        <v>0.4</v>
+      </c>
+      <c r="O24" s="27">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D25" s="31">
+        <v>2.3E-3</v>
+      </c>
+      <c r="E25" s="31">
+        <v>2E-3</v>
+      </c>
+      <c r="F25" s="31">
+        <v>2E-3</v>
+      </c>
+      <c r="G25" s="31">
+        <v>1.9E-3</v>
+      </c>
+      <c r="H25" s="31">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="I25" s="31">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="J25" s="31">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="K25" s="31">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="L25" s="31">
+        <v>1.8E-3</v>
+      </c>
+      <c r="M25" s="31">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="N25" s="31">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="O25" s="31">
+        <v>1.6000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="D26" s="32">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="E26" s="32">
+        <v>0.68799999999999994</v>
+      </c>
+      <c r="F26" s="32">
+        <v>0.66200000000000003</v>
+      </c>
+      <c r="G26" s="32">
+        <v>0.65500000000000003</v>
+      </c>
+      <c r="H26" s="32">
+        <v>0.65500000000000003</v>
+      </c>
+      <c r="I26" s="32">
+        <v>0.623</v>
+      </c>
+      <c r="J26" s="32">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="K26" s="32">
+        <v>0.64900000000000002</v>
+      </c>
+      <c r="L26" s="32">
+        <v>0.65600000000000003</v>
+      </c>
+      <c r="M26" s="32">
+        <v>0.64599999999999991</v>
+      </c>
+      <c r="N26" s="32">
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="O26" s="32">
+        <v>0.59599999999999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D27" s="32">
+        <v>0.81899999999999995</v>
+      </c>
+      <c r="E27" s="32">
+        <v>0.83699999999999997</v>
+      </c>
+      <c r="F27" s="32">
+        <v>0.82399999999999995</v>
+      </c>
+      <c r="G27" s="32">
+        <v>0.79500000000000004</v>
+      </c>
+      <c r="H27" s="32">
+        <v>0.78800000000000003</v>
+      </c>
+      <c r="I27" s="32">
+        <v>0.76100000000000001</v>
+      </c>
+      <c r="J27" s="32">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="K27" s="32">
+        <v>0.78700000000000003</v>
+      </c>
+      <c r="L27" s="32">
+        <v>0.76200000000000001</v>
+      </c>
+      <c r="M27" s="32">
+        <v>0.76900000000000002</v>
+      </c>
+      <c r="N27" s="32">
+        <v>0.73799999999999999</v>
+      </c>
+      <c r="O27" s="32">
+        <v>0.72400000000000009</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D28" s="8">
+        <v>44932</v>
+      </c>
+      <c r="E28" s="8">
+        <v>39015</v>
+      </c>
+      <c r="F28" s="8">
+        <v>39749</v>
+      </c>
+      <c r="G28" s="8">
+        <v>40222</v>
+      </c>
+      <c r="H28" s="8">
+        <v>30524</v>
+      </c>
+      <c r="I28" s="8">
+        <v>32691</v>
+      </c>
+      <c r="J28" s="8">
+        <v>34265</v>
+      </c>
+      <c r="K28" s="8">
+        <v>44805</v>
+      </c>
+      <c r="L28" s="8">
+        <v>35402</v>
+      </c>
+      <c r="M28" s="8">
+        <v>35087</v>
+      </c>
+      <c r="N28" s="8">
+        <v>37131</v>
+      </c>
+      <c r="O28" s="8">
+        <v>32890</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="D29" s="8">
+        <v>39093</v>
+      </c>
+      <c r="E29" s="8">
+        <v>42728</v>
+      </c>
+      <c r="F29" s="8">
+        <v>54134</v>
+      </c>
+      <c r="G29" s="8">
+        <v>53222</v>
+      </c>
+      <c r="H29" s="8">
+        <v>33215</v>
+      </c>
+      <c r="I29" s="8">
+        <v>41119</v>
+      </c>
+      <c r="J29" s="8">
+        <v>39554</v>
+      </c>
+      <c r="K29" s="8">
+        <v>40503</v>
+      </c>
+      <c r="L29" s="8">
+        <v>48317</v>
+      </c>
+      <c r="M29" s="8">
+        <v>38609</v>
+      </c>
+      <c r="N29" s="8">
+        <v>42993</v>
+      </c>
+      <c r="O29" s="8">
+        <v>37660</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D30" s="8">
+        <v>20558</v>
+      </c>
+      <c r="E30" s="8">
+        <v>17352</v>
+      </c>
+      <c r="F30" s="8">
+        <v>19045</v>
+      </c>
+      <c r="G30" s="8">
+        <v>16909</v>
+      </c>
+      <c r="H30" s="8">
+        <v>13355</v>
+      </c>
+      <c r="I30" s="8">
+        <v>13787</v>
+      </c>
+      <c r="J30" s="8">
+        <v>15026</v>
+      </c>
+      <c r="K30" s="8">
+        <v>19695</v>
+      </c>
+      <c r="L30" s="8">
+        <v>14331</v>
+      </c>
+      <c r="M30" s="8">
+        <v>13549</v>
+      </c>
+      <c r="N30" s="8">
+        <v>13694</v>
+      </c>
+      <c r="O30" s="8">
+        <v>12769</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D31" s="8">
+        <v>40204</v>
+      </c>
+      <c r="E31" s="8">
+        <v>41597</v>
+      </c>
+      <c r="F31" s="8">
+        <v>56245</v>
+      </c>
+      <c r="G31" s="8">
+        <v>49444</v>
+      </c>
+      <c r="H31" s="8">
+        <v>38990</v>
+      </c>
+      <c r="I31" s="8">
+        <v>37470</v>
+      </c>
+      <c r="J31" s="8">
+        <v>42873</v>
+      </c>
+      <c r="K31" s="8">
+        <v>33127</v>
+      </c>
+      <c r="L31" s="8">
+        <v>45132</v>
+      </c>
+      <c r="M31" s="8">
+        <v>31402</v>
+      </c>
+      <c r="N31" s="8">
+        <v>45968</v>
+      </c>
+      <c r="O31" s="8">
+        <v>47887</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="D32" s="8">
+        <v>19449</v>
+      </c>
+      <c r="E32" s="8">
+        <v>18923</v>
+      </c>
+      <c r="F32" s="8">
+        <v>19647</v>
+      </c>
+      <c r="G32" s="8">
+        <v>15374</v>
+      </c>
+      <c r="H32" s="8">
+        <v>15332</v>
+      </c>
+      <c r="I32" s="8">
+        <v>12831</v>
+      </c>
+      <c r="J32" s="8">
+        <v>15385</v>
+      </c>
+      <c r="K32" s="8">
+        <v>16562</v>
+      </c>
+      <c r="L32" s="8">
+        <v>15622</v>
+      </c>
+      <c r="M32" s="8">
+        <v>11705</v>
+      </c>
+      <c r="N32" s="8">
+        <v>14209</v>
+      </c>
+      <c r="O32" s="8">
+        <v>16361</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="D33" s="8">
+        <v>1456</v>
+      </c>
+      <c r="E33" s="8">
+        <v>1335</v>
+      </c>
+      <c r="F33" s="8">
+        <v>1204</v>
+      </c>
+      <c r="G33" s="8">
+        <v>1352</v>
+      </c>
+      <c r="H33" s="8">
+        <v>1446</v>
+      </c>
+      <c r="I33" s="8">
+        <v>1410</v>
+      </c>
+      <c r="J33" s="8">
+        <v>1360</v>
+      </c>
+      <c r="K33" s="8">
+        <v>1529</v>
+      </c>
+      <c r="L33" s="8">
+        <v>1552</v>
+      </c>
+      <c r="M33" s="8">
+        <v>1703</v>
+      </c>
+      <c r="N33" s="8">
+        <v>1899</v>
+      </c>
+      <c r="O33" s="8">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="D34" s="27">
+        <v>3.77</v>
+      </c>
+      <c r="E34" s="27">
+        <v>2.19</v>
+      </c>
+      <c r="F34" s="27">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="G34" s="27">
+        <v>3.43</v>
+      </c>
+      <c r="H34" s="27">
+        <v>3.42</v>
+      </c>
+      <c r="I34" s="27">
+        <v>2.56</v>
+      </c>
+      <c r="J34" s="27">
+        <v>2.99</v>
+      </c>
+      <c r="K34" s="27">
+        <v>3</v>
+      </c>
+      <c r="L34" s="27">
+        <v>3.12</v>
+      </c>
+      <c r="M34" s="27">
+        <v>3.79</v>
+      </c>
+      <c r="N34" s="27">
+        <v>3.37</v>
+      </c>
+      <c r="O34" s="27">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+    </row>
+    <row r="36" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="D36" s="8">
+        <v>647</v>
+      </c>
+      <c r="E36" s="8">
+        <v>961</v>
+      </c>
+      <c r="F36" s="8">
+        <v>729</v>
+      </c>
+      <c r="G36" s="8">
+        <v>790</v>
+      </c>
+      <c r="H36" s="8">
+        <v>1124</v>
+      </c>
+      <c r="I36" s="8">
+        <v>1255</v>
+      </c>
+      <c r="J36" s="8">
+        <v>1050</v>
+      </c>
+      <c r="K36" s="8">
+        <v>946</v>
+      </c>
+      <c r="L36" s="8">
+        <v>954</v>
+      </c>
+      <c r="M36" s="8">
+        <v>1102</v>
+      </c>
+      <c r="N36" s="8">
+        <v>1138</v>
+      </c>
+      <c r="O36" s="8">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="D37" s="8">
+        <v>15</v>
+      </c>
+      <c r="E37" s="8">
+        <v>1245</v>
+      </c>
+      <c r="F37" s="8">
+        <v>615</v>
+      </c>
+      <c r="G37" s="8">
+        <v>629</v>
+      </c>
+      <c r="H37" s="8">
+        <v>914</v>
+      </c>
+      <c r="I37" s="8">
+        <v>1599</v>
+      </c>
+      <c r="J37" s="8">
+        <v>1150</v>
+      </c>
+      <c r="K37" s="8">
+        <v>946</v>
+      </c>
+      <c r="L37" s="8">
+        <v>688</v>
+      </c>
+      <c r="M37" s="8">
+        <v>1234</v>
+      </c>
+      <c r="N37" s="8">
+        <v>1318</v>
+      </c>
+      <c r="O37" s="8">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="D38" s="8">
+        <v>819</v>
+      </c>
+      <c r="E38" s="8">
+        <v>1286</v>
+      </c>
+      <c r="F38" s="8">
+        <v>865</v>
+      </c>
+      <c r="G38" s="8">
+        <v>950</v>
+      </c>
+      <c r="H38" s="8">
+        <v>1134</v>
+      </c>
+      <c r="I38" s="8">
+        <v>1529</v>
+      </c>
+      <c r="J38" s="8">
+        <v>1245</v>
+      </c>
+      <c r="K38" s="8">
+        <v>1237</v>
+      </c>
+      <c r="L38" s="8">
+        <v>1044</v>
+      </c>
+      <c r="M38" s="8">
+        <v>1449</v>
+      </c>
+      <c r="N38" s="8">
+        <v>1526</v>
+      </c>
+      <c r="O38" s="8">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="D39" s="27">
+        <v>1.68</v>
+      </c>
+      <c r="E39" s="27">
+        <v>1.58</v>
+      </c>
+      <c r="F39" s="27">
+        <v>1.51</v>
+      </c>
+      <c r="G39" s="27">
+        <v>2</v>
+      </c>
+      <c r="H39" s="27">
+        <v>2.66</v>
+      </c>
+      <c r="I39" s="27">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="J39" s="27">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="K39" s="27">
+        <v>1.86</v>
+      </c>
+      <c r="L39" s="27">
+        <v>1.92</v>
+      </c>
+      <c r="M39" s="27">
+        <v>2.46</v>
+      </c>
+      <c r="N39" s="27">
+        <v>1.99</v>
+      </c>
+      <c r="O39" s="27">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="D40" s="27">
+        <v>2.11</v>
+      </c>
+      <c r="E40" s="27">
+        <v>2.1</v>
+      </c>
+      <c r="F40" s="27">
+        <v>1.78</v>
+      </c>
+      <c r="G40" s="27">
+        <v>2.4</v>
+      </c>
+      <c r="H40" s="27">
+        <v>2.67</v>
+      </c>
+      <c r="I40" s="27">
+        <v>2.77</v>
+      </c>
+      <c r="J40" s="27">
+        <v>2.73</v>
+      </c>
+      <c r="K40" s="27">
+        <v>2.42</v>
+      </c>
+      <c r="L40" s="27">
+        <v>2.09</v>
+      </c>
+      <c r="M40" s="27">
+        <v>3.21</v>
+      </c>
+      <c r="N40" s="27">
+        <v>2.69</v>
+      </c>
+      <c r="O40" s="27">
+        <v>2.12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="27">
+        <v>2.73</v>
+      </c>
+      <c r="H41" s="27">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="I41" s="27">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="J41" s="27">
+        <v>2.14</v>
+      </c>
+      <c r="K41" s="27">
+        <v>2.16</v>
+      </c>
+      <c r="L41" s="27">
+        <v>2.27</v>
+      </c>
+      <c r="M41" s="27">
+        <v>2.67</v>
+      </c>
+      <c r="N41" s="27">
+        <v>2.58</v>
+      </c>
+      <c r="O41" s="27">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="27">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="H42" s="27">
+        <v>7.11</v>
+      </c>
+      <c r="I42" s="27">
+        <v>5.66</v>
+      </c>
+      <c r="J42" s="27">
+        <v>6.31</v>
+      </c>
+      <c r="K42" s="27">
+        <v>4.96</v>
+      </c>
+      <c r="L42" s="27">
+        <v>6.07</v>
+      </c>
+      <c r="M42" s="27">
+        <v>5.14</v>
+      </c>
+      <c r="N42" s="27">
+        <v>5.5</v>
+      </c>
+      <c r="O42" s="27">
+        <v>4.66</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="27">
+        <v>2.77</v>
+      </c>
+      <c r="H43" s="27">
+        <v>2.8</v>
+      </c>
+      <c r="I43" s="27">
+        <v>2.04</v>
+      </c>
+      <c r="J43" s="27">
+        <v>2.31</v>
+      </c>
+      <c r="K43" s="27">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="L43" s="27">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="M43" s="27">
+        <v>2.72</v>
+      </c>
+      <c r="N43" s="27">
+        <v>2.44</v>
+      </c>
+      <c r="O43" s="27">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="27">
+        <v>12.71</v>
+      </c>
+      <c r="H44" s="27">
+        <v>15.95</v>
+      </c>
+      <c r="I44" s="27">
+        <v>12.84</v>
+      </c>
+      <c r="J44" s="27">
+        <v>13.72</v>
+      </c>
+      <c r="K44" s="27">
+        <v>12.03</v>
+      </c>
+      <c r="L44" s="27">
+        <v>13.72</v>
+      </c>
+      <c r="M44" s="27">
+        <v>14.04</v>
+      </c>
+      <c r="N44" s="27">
+        <v>13.42</v>
+      </c>
+      <c r="O44" s="27">
+        <v>12.97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="6"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="15"/>
+      <c r="L45" s="15"/>
+      <c r="M45" s="15"/>
+      <c r="N45" s="15"/>
+      <c r="O45" s="15"/>
+    </row>
+    <row r="46" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="23"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="D46" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" s="25"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="25"/>
+      <c r="H46" s="25"/>
+      <c r="I46" s="25"/>
+      <c r="J46" s="25"/>
+      <c r="K46" s="25"/>
+      <c r="L46" s="25"/>
+      <c r="M46" s="25"/>
+      <c r="N46" s="25"/>
+      <c r="O46" s="25"/>
+    </row>
+    <row r="47" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="D47" s="28">
+        <v>89.7</v>
+      </c>
+      <c r="E47" s="28">
+        <v>73.599999999999994</v>
+      </c>
+      <c r="F47" s="28">
+        <v>43.3</v>
+      </c>
+      <c r="G47" s="28">
+        <v>63.5</v>
+      </c>
+      <c r="H47" s="28">
+        <v>20.8</v>
+      </c>
+      <c r="I47" s="28">
+        <v>80.900000000000006</v>
+      </c>
+      <c r="J47" s="28">
+        <v>33.4</v>
+      </c>
+      <c r="K47" s="28">
+        <v>26.5</v>
+      </c>
+      <c r="L47" s="28">
+        <v>27.6</v>
+      </c>
+      <c r="M47" s="28">
+        <v>21.6</v>
+      </c>
+      <c r="N47" s="28">
+        <v>35.6</v>
+      </c>
+      <c r="O47" s="28">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D48" s="26">
+        <v>20.5</v>
+      </c>
+      <c r="E48" s="26">
+        <v>-13.8</v>
+      </c>
+      <c r="F48" s="26">
+        <v>-1.2</v>
+      </c>
+      <c r="G48" s="26">
+        <v>-2.5</v>
+      </c>
+      <c r="H48" s="26">
+        <v>-5.4</v>
+      </c>
+      <c r="I48" s="26">
+        <v>4.8</v>
+      </c>
+      <c r="J48" s="26">
+        <v>7.7</v>
+      </c>
+      <c r="K48" s="26">
+        <v>-7.1</v>
+      </c>
+      <c r="L48" s="26">
+        <v>-4.7</v>
+      </c>
+      <c r="M48" s="26">
+        <v>14.4</v>
+      </c>
+      <c r="N48" s="26">
+        <v>5.4</v>
+      </c>
+      <c r="O48" s="26">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="D49" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J49" s="26">
+        <v>0.7</v>
+      </c>
+      <c r="K49" s="26">
+        <v>-0.2</v>
+      </c>
+      <c r="L49" s="26">
+        <v>-0.1</v>
+      </c>
+      <c r="M49" s="14"/>
+      <c r="N49" s="14"/>
+      <c r="O49" s="14"/>
+    </row>
+    <row r="50" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="D50" s="26">
+        <v>5.8</v>
+      </c>
+      <c r="E50" s="26">
+        <v>0.6</v>
+      </c>
+      <c r="F50" s="26">
+        <v>-6.4</v>
+      </c>
+      <c r="G50" s="26">
+        <v>0.3</v>
+      </c>
+      <c r="H50" s="26">
+        <v>-0.4</v>
+      </c>
+      <c r="I50" s="26">
+        <v>2.8</v>
+      </c>
+      <c r="J50" s="26">
+        <v>6.7</v>
+      </c>
+      <c r="K50" s="26">
+        <v>5.9</v>
+      </c>
+      <c r="L50" s="26">
+        <v>4.8</v>
+      </c>
+      <c r="M50" s="26">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="N50" s="26">
+        <v>24.8</v>
+      </c>
+      <c r="O50" s="26">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D51" s="26">
+        <v>-74.5</v>
+      </c>
+      <c r="E51" s="26">
+        <v>45.5</v>
+      </c>
+      <c r="F51" s="26">
+        <v>-14.7</v>
+      </c>
+      <c r="G51" s="26">
+        <v>-14.7</v>
+      </c>
+      <c r="H51" s="26">
+        <v>57.4</v>
+      </c>
+      <c r="I51" s="26">
+        <v>-43.8</v>
+      </c>
+      <c r="J51" s="26">
+        <v>23.5</v>
+      </c>
+      <c r="K51" s="26">
+        <v>14.7</v>
+      </c>
+      <c r="L51" s="26">
+        <v>-18.7</v>
+      </c>
+      <c r="M51" s="14"/>
+      <c r="N51" s="26">
+        <v>-29.8</v>
+      </c>
+      <c r="O51" s="26">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="D52" s="26">
+        <v>-17.600000000000001</v>
+      </c>
+      <c r="E52" s="14"/>
+      <c r="F52" s="26">
+        <v>23.3</v>
+      </c>
+      <c r="G52" s="26">
+        <v>-12.4</v>
+      </c>
+      <c r="H52" s="26">
+        <v>-1.8</v>
+      </c>
+      <c r="I52" s="26">
+        <v>-5.5</v>
+      </c>
+      <c r="J52" s="26">
+        <v>-16.100000000000001</v>
+      </c>
+      <c r="K52" s="26">
+        <v>-22.1</v>
+      </c>
+      <c r="L52" s="26">
+        <v>8.9</v>
+      </c>
+      <c r="M52" s="26">
+        <v>-8.6</v>
+      </c>
+      <c r="N52" s="26">
+        <v>4.2</v>
+      </c>
+      <c r="O52" s="26">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D53" s="26">
+        <v>6</v>
+      </c>
+      <c r="E53" s="26">
+        <v>-9.5</v>
+      </c>
+      <c r="F53" s="26">
+        <v>-13.3</v>
+      </c>
+      <c r="G53" s="26">
+        <v>0.2</v>
+      </c>
+      <c r="H53" s="26">
+        <v>-26</v>
+      </c>
+      <c r="I53" s="26">
+        <v>-6.5</v>
+      </c>
+      <c r="J53" s="26">
+        <v>-9.6999999999999993</v>
+      </c>
+      <c r="K53" s="26">
+        <v>7.7</v>
+      </c>
+      <c r="L53" s="26">
+        <v>11.6</v>
+      </c>
+      <c r="M53" s="14"/>
+      <c r="N53" s="26">
+        <v>2.8</v>
+      </c>
+      <c r="O53" s="26">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="D54" s="26">
+        <v>-9.1</v>
+      </c>
+      <c r="E54" s="14"/>
+      <c r="F54" s="26">
+        <v>2.9</v>
+      </c>
+      <c r="G54" s="26">
+        <v>-6.5</v>
+      </c>
+      <c r="H54" s="26">
+        <v>-15.5</v>
+      </c>
+      <c r="I54" s="26">
+        <v>-13.3</v>
+      </c>
+      <c r="J54" s="26">
+        <v>-10.6</v>
+      </c>
+      <c r="K54" s="26">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L54" s="26">
+        <v>1</v>
+      </c>
+      <c r="M54" s="26">
+        <v>-2.9</v>
+      </c>
+      <c r="N54" s="26">
+        <v>-3.5</v>
+      </c>
+      <c r="O54" s="26">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="D55" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E55" s="26">
+        <v>-13.7</v>
+      </c>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="14"/>
+      <c r="L55" s="14"/>
+      <c r="M55" s="14"/>
+      <c r="N55" s="14"/>
+      <c r="O55" s="14"/>
+    </row>
+    <row r="56" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="D56" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E56" s="26">
+        <v>-1.8</v>
+      </c>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="14"/>
+      <c r="L56" s="14"/>
+      <c r="M56" s="14"/>
+      <c r="N56" s="14"/>
+      <c r="O56" s="14"/>
+    </row>
+    <row r="57" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="D57" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E57" s="14"/>
+      <c r="F57" s="26">
+        <v>-1.5</v>
+      </c>
+      <c r="G57" s="26">
+        <v>-1.5</v>
+      </c>
+      <c r="H57" s="26">
+        <v>-1.6</v>
+      </c>
+      <c r="I57" s="14"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="14"/>
+      <c r="L57" s="14"/>
+      <c r="M57" s="26">
+        <v>-1.2</v>
+      </c>
+      <c r="N57" s="14"/>
+      <c r="O57" s="14"/>
+    </row>
+    <row r="58" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D58" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E58" s="14"/>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="14"/>
+      <c r="L58" s="14"/>
+      <c r="M58" s="26">
+        <v>-3.6</v>
+      </c>
+      <c r="N58" s="26">
+        <v>0.7</v>
+      </c>
+      <c r="O58" s="26">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D59" s="28">
+        <v>20.8</v>
+      </c>
+      <c r="E59" s="28">
+        <v>80.900000000000006</v>
+      </c>
+      <c r="F59" s="28">
+        <v>32.5</v>
+      </c>
+      <c r="G59" s="28">
+        <v>26.5</v>
+      </c>
+      <c r="H59" s="28">
+        <v>27.6</v>
+      </c>
+      <c r="I59" s="28">
+        <v>21.6</v>
+      </c>
+      <c r="J59" s="28">
+        <v>35.6</v>
+      </c>
+      <c r="K59" s="28">
+        <v>29.1</v>
+      </c>
+      <c r="L59" s="28">
+        <v>30</v>
+      </c>
+      <c r="M59" s="28">
+        <v>29</v>
+      </c>
+      <c r="N59" s="28">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="O59" s="28">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="6"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E60" s="15"/>
+      <c r="F60" s="15"/>
+      <c r="G60" s="15"/>
+      <c r="H60" s="15"/>
+      <c r="I60" s="15"/>
+      <c r="J60" s="15"/>
+      <c r="K60" s="15"/>
+      <c r="L60" s="15"/>
+      <c r="M60" s="15"/>
+      <c r="N60" s="15"/>
+      <c r="O60" s="15"/>
+    </row>
+    <row r="61" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="23"/>
+      <c r="B61" s="23"/>
+      <c r="C61" s="24" t="s">
+        <v>266</v>
+      </c>
+      <c r="D61" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E61" s="25"/>
+      <c r="F61" s="25"/>
+      <c r="G61" s="25"/>
+      <c r="H61" s="25"/>
+      <c r="I61" s="25"/>
+      <c r="J61" s="25"/>
+      <c r="K61" s="25"/>
+      <c r="L61" s="25"/>
+      <c r="M61" s="25"/>
+      <c r="N61" s="25"/>
+      <c r="O61" s="25"/>
+    </row>
+    <row r="62" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="D62" s="10">
+        <v>367</v>
+      </c>
+      <c r="E62" s="10">
+        <v>486</v>
+      </c>
+      <c r="F62" s="10">
+        <v>727</v>
+      </c>
+      <c r="G62" s="10">
+        <v>518</v>
+      </c>
+      <c r="H62" s="10">
+        <v>15</v>
+      </c>
+      <c r="I62" s="10">
+        <v>1245</v>
+      </c>
+      <c r="J62" s="10">
+        <v>615</v>
+      </c>
+      <c r="K62" s="10">
+        <v>629</v>
+      </c>
+      <c r="L62" s="10">
+        <v>914</v>
+      </c>
+      <c r="M62" s="10">
+        <v>1599</v>
+      </c>
+      <c r="N62" s="10">
+        <v>1150</v>
+      </c>
+      <c r="O62" s="10">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D63" s="8">
+        <v>-186</v>
+      </c>
+      <c r="E63" s="8">
+        <v>205</v>
+      </c>
+      <c r="F63" s="8">
+        <v>343</v>
+      </c>
+      <c r="G63" s="8">
+        <v>-3</v>
+      </c>
+      <c r="H63" s="8">
+        <v>647</v>
+      </c>
+      <c r="I63" s="8">
+        <v>156</v>
+      </c>
+      <c r="J63" s="8">
+        <v>173</v>
+      </c>
+      <c r="K63" s="8">
+        <v>-156</v>
+      </c>
+      <c r="L63" s="8">
+        <v>-297</v>
+      </c>
+      <c r="M63" s="8">
+        <v>-16</v>
+      </c>
+      <c r="N63" s="8">
+        <v>-122</v>
+      </c>
+      <c r="O63" s="8">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D64" s="8">
+        <v>-210</v>
+      </c>
+      <c r="E64" s="8">
+        <v>302</v>
+      </c>
+      <c r="F64" s="8">
+        <v>-49</v>
+      </c>
+      <c r="G64" s="8">
+        <v>154</v>
+      </c>
+      <c r="H64" s="8">
+        <v>520</v>
+      </c>
+      <c r="I64" s="8">
+        <v>207</v>
+      </c>
+      <c r="J64" s="8">
+        <v>53</v>
+      </c>
+      <c r="K64" s="8">
+        <v>61</v>
+      </c>
+      <c r="L64" s="8">
+        <v>95</v>
+      </c>
+      <c r="M64" s="8">
+        <v>-537</v>
+      </c>
+      <c r="N64" s="8">
+        <v>33</v>
+      </c>
+      <c r="O64" s="8">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="D65" s="8">
+        <v>3</v>
+      </c>
+      <c r="E65" s="8">
+        <v>237</v>
+      </c>
+      <c r="F65" s="8">
+        <v>-283</v>
+      </c>
+      <c r="G65" s="8">
+        <v>99</v>
+      </c>
+      <c r="H65" s="8">
+        <v>27</v>
+      </c>
+      <c r="I65" s="8">
+        <v>158</v>
+      </c>
+      <c r="J65" s="8">
+        <v>272</v>
+      </c>
+      <c r="K65" s="8">
+        <v>312</v>
+      </c>
+      <c r="L65" s="8">
+        <v>-108</v>
+      </c>
+      <c r="M65" s="8">
+        <v>112</v>
+      </c>
+      <c r="N65" s="8">
+        <v>-47</v>
+      </c>
+      <c r="O65" s="8">
+        <v>-122</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="D66" s="8">
+        <v>19</v>
+      </c>
+      <c r="E66" s="8">
+        <v>24</v>
+      </c>
+      <c r="F66" s="8">
+        <v>5</v>
+      </c>
+      <c r="G66" s="8">
+        <v>7</v>
+      </c>
+      <c r="H66" s="8">
+        <v>2</v>
+      </c>
+      <c r="I66" s="8">
+        <v>5</v>
+      </c>
+      <c r="J66" s="8">
+        <v>-9</v>
+      </c>
+      <c r="K66" s="8">
+        <v>-12</v>
+      </c>
+      <c r="L66" s="8">
+        <v>10</v>
+      </c>
+      <c r="M66" s="8">
+        <v>-16</v>
+      </c>
+      <c r="N66" s="8">
+        <v>-3</v>
+      </c>
+      <c r="O66" s="8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="D67" s="8">
+        <v>-5</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-26</v>
+      </c>
+      <c r="F67" s="8">
+        <v>6</v>
+      </c>
+      <c r="G67" s="8"/>
+      <c r="H67" s="8"/>
+      <c r="I67" s="8"/>
+      <c r="J67" s="8"/>
+      <c r="K67" s="8"/>
+      <c r="L67" s="8"/>
+      <c r="M67" s="8"/>
+      <c r="N67" s="8"/>
+      <c r="O67" s="8"/>
+    </row>
+    <row r="68" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E68" s="8"/>
+      <c r="F68" s="8"/>
+      <c r="G68" s="8">
+        <v>28</v>
+      </c>
+      <c r="H68" s="8">
+        <v>-28</v>
+      </c>
+      <c r="I68" s="8">
+        <v>-4</v>
+      </c>
+      <c r="J68" s="8">
+        <v>9</v>
+      </c>
+      <c r="K68" s="8">
+        <v>-20</v>
+      </c>
+      <c r="L68" s="8">
+        <v>12</v>
+      </c>
+      <c r="M68" s="8">
+        <v>-21</v>
+      </c>
+      <c r="N68" s="8">
+        <v>23</v>
+      </c>
+      <c r="O68" s="8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="D69" s="8">
+        <v>26</v>
+      </c>
+      <c r="E69" s="8">
+        <v>17</v>
+      </c>
+      <c r="F69" s="8">
+        <v>-132</v>
+      </c>
+      <c r="G69" s="8">
+        <v>-174</v>
+      </c>
+      <c r="H69" s="8">
+        <v>-269</v>
+      </c>
+      <c r="I69" s="8">
+        <v>-168</v>
+      </c>
+      <c r="J69" s="8">
+        <v>37</v>
+      </c>
+      <c r="K69" s="8">
+        <v>132</v>
+      </c>
+      <c r="L69" s="8">
+        <v>62</v>
+      </c>
+      <c r="M69" s="8">
+        <v>112</v>
+      </c>
+      <c r="N69" s="8">
+        <v>284</v>
+      </c>
+      <c r="O69" s="8">
+        <v>-260</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D70" s="10">
+        <v>15</v>
+      </c>
+      <c r="E70" s="10">
+        <v>1245</v>
+      </c>
+      <c r="F70" s="10">
+        <v>615</v>
+      </c>
+      <c r="G70" s="10">
+        <v>629</v>
+      </c>
+      <c r="H70" s="10">
+        <v>914</v>
+      </c>
+      <c r="I70" s="10">
+        <v>1599</v>
+      </c>
+      <c r="J70" s="10">
+        <v>1150</v>
+      </c>
+      <c r="K70" s="10">
+        <v>946</v>
+      </c>
+      <c r="L70" s="10">
+        <v>688</v>
+      </c>
+      <c r="M70" s="10">
+        <v>1234</v>
+      </c>
+      <c r="N70" s="10">
+        <v>1318</v>
+      </c>
+      <c r="O70" s="10">
+        <v>1114</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9117E93F-4FAC-042A-B07E-6BCC9A0DDCF5}">
+  <dimension ref="A1:O49"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.36328125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="25" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="3" max="3" width="66.6328125" style="13" customWidth="1" collapsed="1"/>
+    <col min="4" max="15" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="25"/>
+    </row>
+    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+    </row>
+    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>228</v>
       </c>
       <c r="D6" s="26">
@@ -13936,14 +13949,14 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25C6C835-3496-E519-F714-0CE59CC56309}">
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.36328125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="25" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="66.6640625" style="13" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="66.6328125" style="13" customWidth="1" collapsed="1"/>
     <col min="4" max="6" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -13963,7 +13976,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
@@ -13977,7 +13990,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
@@ -14506,14 +14519,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9F1E29E-188A-2417-7381-9280524B0C83}">
   <dimension ref="A1:F148"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.36328125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="25" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="66.6640625" style="13" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="66.6328125" style="13" customWidth="1" collapsed="1"/>
     <col min="4" max="6" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -14533,7 +14546,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
@@ -14547,7 +14560,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
@@ -16882,14 +16895,14 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDCCA8EA-7727-482F-524F-C566FE379A81}">
   <dimension ref="A1:F259"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.36328125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="25" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="66.6640625" style="13" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="66.6328125" style="13" customWidth="1" collapsed="1"/>
     <col min="4" max="6" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -16909,7 +16922,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
@@ -16923,7 +16936,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
@@ -21190,14 +21203,14 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F06F577-D94C-EECD-80E7-5C38471494C4}">
   <dimension ref="A1:F510"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.36328125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="25" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="66.6640625" style="13" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="66.6328125" style="13" customWidth="1" collapsed="1"/>
     <col min="4" max="6" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -21217,7 +21230,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
@@ -21233,7 +21246,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
@@ -30201,14 +30214,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D60A5B5E-46B6-55ED-A30C-4125D10E7AFD}">
   <dimension ref="A1:O47"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.36328125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="25" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="66.6640625" style="13" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="66.6328125" style="13" customWidth="1" collapsed="1"/>
     <col min="4" max="15" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -30255,7 +30268,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
@@ -30298,7 +30311,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
@@ -31907,14 +31920,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDBAEC29-F3CC-7BCA-B034-11BC9B7F66EE}">
   <dimension ref="A1:F39"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.36328125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="25" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="66.6640625" style="13" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="66.6328125" style="13" customWidth="1" collapsed="1"/>
     <col min="4" max="6" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -31934,7 +31947,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
@@ -31950,7 +31963,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
@@ -32614,14 +32627,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3647A5A8-B315-AD61-5172-544A86EFEFBD}">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.36328125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="25" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="66.6640625" style="13" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="66.6328125" style="13" customWidth="1" collapsed="1"/>
     <col min="4" max="15" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -32668,7 +32681,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
@@ -32711,7 +32724,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
@@ -34193,14 +34206,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE93E265-084C-8F7A-BCA6-687D8EBD592D}">
   <dimension ref="A1:F41"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.36328125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="25" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="66.6640625" style="13" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="66.6328125" style="13" customWidth="1" collapsed="1"/>
     <col min="4" max="6" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -34220,7 +34233,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
@@ -34236,7 +34249,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
@@ -34988,14 +35001,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F1FCF8B-657F-9CAA-322F-C63E3D525ECF}">
   <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.36328125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="25" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="66.6640625" style="13" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="66.6328125" style="13" customWidth="1" collapsed="1"/>
     <col min="4" max="15" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -35042,7 +35055,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
@@ -35085,7 +35098,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
@@ -36761,14 +36774,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07244862-1876-8E1D-FFEC-C394621FABF3}">
   <dimension ref="A1:F207"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.36328125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="25" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="66.6640625" style="13" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="66.6328125" style="13" customWidth="1" collapsed="1"/>
     <col min="4" max="6" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -36788,7 +36801,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
@@ -36804,7 +36817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
@@ -40444,14 +40457,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA68676D-9F5D-D4B8-4E77-46EDDB62BF28}">
   <dimension ref="A1:O205"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.36328125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="25" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="66.6640625" style="13" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="66.6328125" style="13" customWidth="1" collapsed="1"/>
     <col min="4" max="15" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -40498,7 +40511,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
@@ -40541,7 +40554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
@@ -48374,14 +48387,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{066C1F79-F0F4-45AA-9171-05B46B01779B}">
   <dimension ref="A1:F66"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.36328125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="25" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="66.6640625" style="13" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="66.6328125" style="13" customWidth="1" collapsed="1"/>
     <col min="4" max="6" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -48401,7 +48414,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
@@ -48417,7 +48430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
